--- a/leads/Hamilton_County_Auto_Glass_Leads.xlsx
+++ b/leads/Hamilton_County_Auto_Glass_Leads.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Leads" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$R$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$R$389</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>285</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -641,7 +641,7 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>• The 'Leads' tab holds all 285 verified prospects with autofilter enabled — filter by Lead Priority, Industry, or City.</t>
+          <t>• The 'Leads' tab holds all 388 verified prospects with autofilter enabled — filter by Lead Priority, Industry, or City.</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R286"/>
+  <dimension ref="A1:R389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -27018,8 +27018,9484 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>Conley Towing</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>Towing</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>5603 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G287" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-3535</t>
+        </is>
+      </c>
+      <c r="I287" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J287" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K287" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L287" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M287" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr">
+        <is>
+          <t>24/7 towing fleet with constant windshield/road-debris exposure</t>
+        </is>
+      </c>
+      <c r="O287" s="8" t="inlineStr">
+        <is>
+          <t>Active BBB/Yellow Pages listing; 24-hr operation</t>
+        </is>
+      </c>
+      <c r="P287" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="Q287" s="8" t="inlineStr">
+        <is>
+          <t>Google Business listing</t>
+        </is>
+      </c>
+      <c r="R287" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>Gudel's Garage and Towing</t>
+        </is>
+      </c>
+      <c r="B288" s="8" t="inlineStr">
+        <is>
+          <t>Towing / Auto Repair</t>
+        </is>
+      </c>
+      <c r="C288" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D288" s="8" t="inlineStr">
+        <is>
+          <t>6403 Middle Valley Rd</t>
+        </is>
+      </c>
+      <c r="E288" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F288" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G288" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H288" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-8010</t>
+        </is>
+      </c>
+      <c r="I288" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J288" s="8" t="inlineStr">
+        <is>
+          <t>gudelsgarageandtowing.com</t>
+        </is>
+      </c>
+      <c r="K288" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L288" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M288" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N288" s="8" t="inlineStr">
+        <is>
+          <t>Combined towing and repair fleet, direct auto-glass complement</t>
+        </is>
+      </c>
+      <c r="O288" s="8" t="inlineStr">
+        <is>
+          <t>Active company website; 24/7 emergency towing</t>
+        </is>
+      </c>
+      <c r="P288" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q288" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R288" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>Maxi Auto Service (Hixson)</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C289" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="inlineStr">
+        <is>
+          <t>5229 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E289" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F289" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G289" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>(423) 877-5569</t>
+        </is>
+      </c>
+      <c r="I289" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J289" s="8" t="inlineStr">
+        <is>
+          <t>maxicarcarehixson.com</t>
+        </is>
+      </c>
+      <c r="K289" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L289" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M289" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N289" s="8" t="inlineStr">
+        <is>
+          <t>Repair shop with towing referral fleet and existing auto-service customer base</t>
+        </is>
+      </c>
+      <c r="O289" s="8" t="inlineStr">
+        <is>
+          <t>Active company website with service listings</t>
+        </is>
+      </c>
+      <c r="P289" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q289" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R289" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>Tennessee Roofing &amp; Construction, Inc.</t>
+        </is>
+      </c>
+      <c r="B290" s="8" t="inlineStr">
+        <is>
+          <t>Roofing / Construction</t>
+        </is>
+      </c>
+      <c r="C290" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D290" s="8" t="inlineStr">
+        <is>
+          <t>8427 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E290" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F290" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G290" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H290" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-8826</t>
+        </is>
+      </c>
+      <c r="I290" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J290" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K290" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L290" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M290" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N290" s="8" t="inlineStr">
+        <is>
+          <t>Commercial roofing crews run multi-truck fleets on job sites since 1994</t>
+        </is>
+      </c>
+      <c r="O290" s="8" t="inlineStr">
+        <is>
+          <t>HBA Chattanooga member listing; active since 1994</t>
+        </is>
+      </c>
+      <c r="P290" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q290" s="8" t="inlineStr">
+        <is>
+          <t>HBA Greater Chattanooga directory</t>
+        </is>
+      </c>
+      <c r="R290" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>HEP Is On The Way</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>HVAC / Plumbing / Electrical</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="inlineStr">
+        <is>
+          <t>6425 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F291" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G291" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>(423) 397-7772</t>
+        </is>
+      </c>
+      <c r="I291" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J291" s="8" t="inlineStr">
+        <is>
+          <t>hepisontheway.com</t>
+        </is>
+      </c>
+      <c r="K291" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L291" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M291" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N291" s="8" t="inlineStr">
+        <is>
+          <t>Large regional service-van fleet (24/7 HVAC/plumbing/electrical/roofing)</t>
+        </is>
+      </c>
+      <c r="O291" s="8" t="inlineStr">
+        <is>
+          <t>27 Yelp reviews; LinkedIn company page; 24/7 operation</t>
+        </is>
+      </c>
+      <c r="P291" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q291" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn company page</t>
+        </is>
+      </c>
+      <c r="R291" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>L&amp;B Lawn &amp; Landscaping</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="C292" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D292" s="8" t="inlineStr">
+        <is>
+          <t>5928 Hixson Pike, Suite A #113</t>
+        </is>
+      </c>
+      <c r="E292" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F292" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G292" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>(423) 715-3751</t>
+        </is>
+      </c>
+      <c r="I292" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J292" s="8" t="inlineStr">
+        <is>
+          <t>lblawnlandscaping.com</t>
+        </is>
+      </c>
+      <c r="K292" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L292" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M292" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N292" s="8" t="inlineStr">
+        <is>
+          <t>Commercial/residential landscaping trucks and trailers exposed to debris</t>
+        </is>
+      </c>
+      <c r="O292" s="8" t="inlineStr">
+        <is>
+          <t>Licensed/insured company site</t>
+        </is>
+      </c>
+      <c r="P292" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q292" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R292" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>Northwest Exterminating (Hixson)</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
+          <t>Pest Control</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D293" s="8" t="inlineStr">
+        <is>
+          <t>1906 Hamill Rd</t>
+        </is>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F293" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G293" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>(423) 877-0111</t>
+        </is>
+      </c>
+      <c r="I293" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J293" s="8" t="inlineStr">
+        <is>
+          <t>northwestexterminating.com</t>
+        </is>
+      </c>
+      <c r="K293" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L293" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M293" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N293" s="8" t="inlineStr">
+        <is>
+          <t>Regional pest control branch runs a daily route-service van fleet</t>
+        </is>
+      </c>
+      <c r="O293" s="8" t="inlineStr">
+        <is>
+          <t>13 Yelp reviews; active branch office</t>
+        </is>
+      </c>
+      <c r="P293" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q293" s="8" t="inlineStr">
+        <is>
+          <t>BBB category listing</t>
+        </is>
+      </c>
+      <c r="R293" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>Peak Pest Control</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
+        <is>
+          <t>Pest Control</t>
+        </is>
+      </c>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D294" s="8" t="inlineStr">
+        <is>
+          <t>5906 Cassandra Smith Rd</t>
+        </is>
+      </c>
+      <c r="E294" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F294" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G294" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H294" s="8" t="inlineStr">
+        <is>
+          <t>(423) 386-5721</t>
+        </is>
+      </c>
+      <c r="I294" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J294" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K294" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L294" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M294" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N294" s="8" t="inlineStr">
+        <is>
+          <t>Route-based service vehicles with likely daily rural-road mileage</t>
+        </is>
+      </c>
+      <c r="O294" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp business listing</t>
+        </is>
+      </c>
+      <c r="P294" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q294" s="8" t="inlineStr">
+        <is>
+          <t>Facebook business page</t>
+        </is>
+      </c>
+      <c r="R294" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>Harvey's Plumbing</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D295" s="8" t="inlineStr">
+        <is>
+          <t>8003 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E295" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F295" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G295" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-0998</t>
+        </is>
+      </c>
+      <c r="I295" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J295" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K295" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L295" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M295" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N295" s="8" t="inlineStr">
+        <is>
+          <t>Emergency plumbing service trucks running daily calls</t>
+        </is>
+      </c>
+      <c r="O295" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with posted hours</t>
+        </is>
+      </c>
+      <c r="P295" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q295" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R295" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="8" t="inlineStr">
+        <is>
+          <t>Precise Plumbing (Hixson)</t>
+        </is>
+      </c>
+      <c r="B296" s="8" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="C296" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D296" s="8" t="inlineStr">
+        <is>
+          <t>8011 Hixson Pike, Ste B</t>
+        </is>
+      </c>
+      <c r="E296" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F296" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G296" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H296" s="8" t="inlineStr">
+        <is>
+          <t>(423) 843-0124</t>
+        </is>
+      </c>
+      <c r="I296" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J296" s="8" t="inlineStr">
+        <is>
+          <t>preciseplumbing.com</t>
+        </is>
+      </c>
+      <c r="K296" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L296" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M296" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N296" s="8" t="inlineStr">
+        <is>
+          <t>Service-van fleet for residential/commercial plumbing calls</t>
+        </is>
+      </c>
+      <c r="O296" s="8" t="inlineStr">
+        <is>
+          <t>Active company website</t>
+        </is>
+      </c>
+      <c r="P296" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q296" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R296" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>Ray's Plumbing</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="C297" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D297" s="8" t="inlineStr">
+        <is>
+          <t>6921 Middle Valley Rd #105</t>
+        </is>
+      </c>
+      <c r="E297" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F297" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G297" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H297" s="8" t="inlineStr">
+        <is>
+          <t>(423) 421-6341</t>
+        </is>
+      </c>
+      <c r="I297" s="8" t="inlineStr">
+        <is>
+          <t>raysplumbingchattanooga@gmail.com</t>
+        </is>
+      </c>
+      <c r="J297" s="8" t="inlineStr">
+        <is>
+          <t>rayplumbingchattanooga.com</t>
+        </is>
+      </c>
+      <c r="K297" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L297" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M297" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N297" s="8" t="inlineStr">
+        <is>
+          <t>24/7 emergency plumbing means high daily mileage on service vans</t>
+        </is>
+      </c>
+      <c r="O297" s="8" t="inlineStr">
+        <is>
+          <t>Published business email and active site</t>
+        </is>
+      </c>
+      <c r="P297" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q297" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R297" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="8" t="inlineStr">
+        <is>
+          <t>Hixson Pike Dental</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D298" s="8" t="inlineStr">
+        <is>
+          <t>5109 Skillern Dr</t>
+        </is>
+      </c>
+      <c r="E298" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F298" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G298" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H298" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-2420</t>
+        </is>
+      </c>
+      <c r="I298" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J298" s="8" t="inlineStr">
+        <is>
+          <t>hixsonpikedental.com</t>
+        </is>
+      </c>
+      <c r="K298" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L298" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M298" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N298" s="8" t="inlineStr">
+        <is>
+          <t>Practice vehicle(s) for staff/courier runs; strong local B2B referral potential</t>
+        </is>
+      </c>
+      <c r="O298" s="8" t="inlineStr">
+        <is>
+          <t>Active practice website with services listed</t>
+        </is>
+      </c>
+      <c r="P298" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q298" s="8" t="inlineStr">
+        <is>
+          <t>CareCredit provider listing</t>
+        </is>
+      </c>
+      <c r="R298" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>True Dental - Hixson</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C299" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D299" s="8" t="inlineStr">
+        <is>
+          <t>4513 Hixson Pike, Ste 103</t>
+        </is>
+      </c>
+      <c r="E299" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F299" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G299" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H299" s="8" t="inlineStr">
+        <is>
+          <t>(423) 875-6778</t>
+        </is>
+      </c>
+      <c r="I299" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J299" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K299" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L299" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M299" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N299" s="8" t="inlineStr">
+        <is>
+          <t>Local practice; potential referral/networking prospect</t>
+        </is>
+      </c>
+      <c r="O299" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with 21 photos</t>
+        </is>
+      </c>
+      <c r="P299" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q299" s="8" t="inlineStr">
+        <is>
+          <t>patientconnect365.com listing</t>
+        </is>
+      </c>
+      <c r="R299" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="8" t="inlineStr">
+        <is>
+          <t>North River Church</t>
+        </is>
+      </c>
+      <c r="B300" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C300" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D300" s="8" t="inlineStr">
+        <is>
+          <t>5954 Highway 153</t>
+        </is>
+      </c>
+      <c r="E300" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F300" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G300" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H300" s="8" t="inlineStr">
+        <is>
+          <t>(423) 870-8397</t>
+        </is>
+      </c>
+      <c r="I300" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J300" s="8" t="inlineStr">
+        <is>
+          <t>northrivercma.org</t>
+        </is>
+      </c>
+      <c r="K300" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L300" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M300" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N300" s="8" t="inlineStr">
+        <is>
+          <t>Congregation vans/buses for ministry transport</t>
+        </is>
+      </c>
+      <c r="O300" s="8" t="inlineStr">
+        <is>
+          <t>Active church website</t>
+        </is>
+      </c>
+      <c r="P300" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q300" s="8" t="inlineStr">
+        <is>
+          <t>ChurchFinder.com directory</t>
+        </is>
+      </c>
+      <c r="R300" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>Christian Brothers Automotive Hixson</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>5595 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F301" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G301" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>(423) 403-3678</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J301" s="8" t="inlineStr">
+        <is>
+          <t>cbac.com/hixson</t>
+        </is>
+      </c>
+      <c r="K301" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L301" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M301" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N301" s="8" t="inlineStr">
+        <is>
+          <t>Franchise auto shop with loaner/shuttle vehicles; natural glass-referral partner</t>
+        </is>
+      </c>
+      <c r="O301" s="8" t="inlineStr">
+        <is>
+          <t>Active franchise location page</t>
+        </is>
+      </c>
+      <c r="P301" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q301" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R301" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>Graham Auto Repair</t>
+        </is>
+      </c>
+      <c r="B302" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C302" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D302" s="8" t="inlineStr">
+        <is>
+          <t>8615 Hixson Pike, Ste 104</t>
+        </is>
+      </c>
+      <c r="E302" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F302" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G302" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H302" s="8" t="inlineStr">
+        <is>
+          <t>(423) 498-4163</t>
+        </is>
+      </c>
+      <c r="I302" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J302" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K302" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L302" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M302" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N302" s="8" t="inlineStr">
+        <is>
+          <t>Independent repair shop; potential subcontract/referral partner</t>
+        </is>
+      </c>
+      <c r="O302" s="8" t="inlineStr">
+        <is>
+          <t>Active Facebook business page</t>
+        </is>
+      </c>
+      <c r="P302" s="8" t="inlineStr">
+        <is>
+          <t>Facebook business page</t>
+        </is>
+      </c>
+      <c r="Q302" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R302" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>S&amp;S Auto Repair</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C303" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D303" s="8" t="inlineStr">
+        <is>
+          <t>4606 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E303" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F303" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G303" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H303" s="8" t="inlineStr">
+        <is>
+          <t>(423) 206-2702</t>
+        </is>
+      </c>
+      <c r="I303" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J303" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K303" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L303" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M303" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N303" s="8" t="inlineStr">
+        <is>
+          <t>Established shop with active reviews; possible glass-referral partner</t>
+        </is>
+      </c>
+      <c r="O303" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with active reviews</t>
+        </is>
+      </c>
+      <c r="P303" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q303" s="8" t="inlineStr">
+        <is>
+          <t>autorepairscore.com listing</t>
+        </is>
+      </c>
+      <c r="R303" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>Protech Automotive</t>
+        </is>
+      </c>
+      <c r="B304" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C304" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D304" s="8" t="inlineStr">
+        <is>
+          <t>6462 Hixson Pike, Ste 100</t>
+        </is>
+      </c>
+      <c r="E304" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F304" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G304" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H304" s="8" t="inlineStr">
+        <is>
+          <t>(423) 847-9727</t>
+        </is>
+      </c>
+      <c r="I304" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J304" s="8" t="inlineStr">
+        <is>
+          <t>protechauto.mechanicnet.com</t>
+        </is>
+      </c>
+      <c r="K304" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L304" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M304" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N304" s="8" t="inlineStr">
+        <is>
+          <t>Independent repair shop; potential glass-referral partner</t>
+        </is>
+      </c>
+      <c r="O304" s="8" t="inlineStr">
+        <is>
+          <t>Active MechanicNet business site</t>
+        </is>
+      </c>
+      <c r="P304" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q304" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R304" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="8" t="inlineStr">
+        <is>
+          <t>Hixson Auto Sales</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>Used Car Dealer</t>
+        </is>
+      </c>
+      <c r="C305" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>5469 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G305" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H305" s="8" t="inlineStr">
+        <is>
+          <t>(423) 847-6530</t>
+        </is>
+      </c>
+      <c r="I305" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J305" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K305" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L305" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M305" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N305" s="8" t="inlineStr">
+        <is>
+          <t>Dealer lot inventory frequently needs windshield replacement before resale</t>
+        </is>
+      </c>
+      <c r="O305" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P305" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q305" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R305" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
+        <is>
+          <t>Car-Mart of Hixson</t>
+        </is>
+      </c>
+      <c r="B306" s="8" t="inlineStr">
+        <is>
+          <t>Used Car Dealer</t>
+        </is>
+      </c>
+      <c r="C306" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D306" s="8" t="inlineStr">
+        <is>
+          <t>4517 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E306" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F306" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G306" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H306" s="8" t="inlineStr">
+        <is>
+          <t>(423) 954-0147</t>
+        </is>
+      </c>
+      <c r="I306" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J306" s="8" t="inlineStr">
+        <is>
+          <t>car-mart.com</t>
+        </is>
+      </c>
+      <c r="K306" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L306" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M306" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N306" s="8" t="inlineStr">
+        <is>
+          <t>National used-car chain location; recon/reconditioning needs include glass</t>
+        </is>
+      </c>
+      <c r="O306" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P306" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q306" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R306" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="8" t="inlineStr">
+        <is>
+          <t>Motivated Movers</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>Moving Company</t>
+        </is>
+      </c>
+      <c r="C307" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D307" s="8" t="inlineStr">
+        <is>
+          <t>5510 TN Highway 153</t>
+        </is>
+      </c>
+      <c r="E307" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F307" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G307" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H307" s="8" t="inlineStr">
+        <is>
+          <t>(423) 994-0529</t>
+        </is>
+      </c>
+      <c r="I307" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J307" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K307" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L307" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M307" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N307" s="8" t="inlineStr">
+        <is>
+          <t>Moving truck fleet exposed to daily road/highway debris</t>
+        </is>
+      </c>
+      <c r="O307" s="8" t="inlineStr">
+        <is>
+          <t>Active Nextdoor business page</t>
+        </is>
+      </c>
+      <c r="P307" s="8" t="inlineStr">
+        <is>
+          <t>Nextdoor business page</t>
+        </is>
+      </c>
+      <c r="Q307" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R307" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="8" t="inlineStr">
+        <is>
+          <t>WesHauls</t>
+        </is>
+      </c>
+      <c r="B308" s="8" t="inlineStr">
+        <is>
+          <t>Moving / Delivery</t>
+        </is>
+      </c>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D308" s="8" t="inlineStr">
+        <is>
+          <t>5450 Hwy 153, Ste 126, Unit 1150</t>
+        </is>
+      </c>
+      <c r="E308" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F308" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G308" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H308" s="8" t="inlineStr">
+        <is>
+          <t>(423) 596-8237</t>
+        </is>
+      </c>
+      <c r="I308" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J308" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K308" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L308" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M308" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N308" s="8" t="inlineStr">
+        <is>
+          <t>Hauling/delivery vehicles on regular routes</t>
+        </is>
+      </c>
+      <c r="O308" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P308" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q308" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R308" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="8" t="inlineStr">
+        <is>
+          <t>Home Pros Painting</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr">
+        <is>
+          <t>Painting Contractor</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>7710 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G309" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H309" s="8" t="inlineStr">
+        <is>
+          <t>(423) 320-6303</t>
+        </is>
+      </c>
+      <c r="I309" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J309" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K309" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L309" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M309" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N309" s="8" t="inlineStr">
+        <is>
+          <t>Crew trucks/trailers for commercial/residential/industrial paint jobs</t>
+        </is>
+      </c>
+      <c r="O309" s="8" t="inlineStr">
+        <is>
+          <t>Active Facebook business page</t>
+        </is>
+      </c>
+      <c r="P309" s="8" t="inlineStr">
+        <is>
+          <t>Facebook business page</t>
+        </is>
+      </c>
+      <c r="Q309" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R309" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="8" t="inlineStr">
+        <is>
+          <t>Chattanooga Paint &amp; Decorating</t>
+        </is>
+      </c>
+      <c r="B310" s="8" t="inlineStr">
+        <is>
+          <t>Paint Supplier / Retail</t>
+        </is>
+      </c>
+      <c r="C310" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D310" s="8" t="inlineStr">
+        <is>
+          <t>5529 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E310" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F310" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G310" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H310" s="8" t="inlineStr">
+        <is>
+          <t>(423) 843-9281</t>
+        </is>
+      </c>
+      <c r="I310" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J310" s="8" t="inlineStr">
+        <is>
+          <t>chattanoogapaint.com</t>
+        </is>
+      </c>
+      <c r="K310" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L310" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M310" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N310" s="8" t="inlineStr">
+        <is>
+          <t>Supply/delivery vehicles for contractor accounts</t>
+        </is>
+      </c>
+      <c r="O310" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="P310" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q310" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R310" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="8" t="inlineStr">
+        <is>
+          <t>Lawson Electric Co</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>Electrical Contractor</t>
+        </is>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>6246 Dayton Blvd</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G311" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>(423) 267-5471</t>
+        </is>
+      </c>
+      <c r="I311" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J311" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K311" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L311" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M311" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N311" s="8" t="inlineStr">
+        <is>
+          <t>Electrical service van fleet with daily job-site travel</t>
+        </is>
+      </c>
+      <c r="O311" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="P311" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="Q311" s="8" t="inlineStr">
+        <is>
+          <t>BBB category listing</t>
+        </is>
+      </c>
+      <c r="R311" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="8" t="inlineStr">
+        <is>
+          <t>Grant-Neil Electric</t>
+        </is>
+      </c>
+      <c r="B312" s="8" t="inlineStr">
+        <is>
+          <t>Electrical Contractor</t>
+        </is>
+      </c>
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D312" s="8" t="inlineStr">
+        <is>
+          <t>6117 Dayton Blvd</t>
+        </is>
+      </c>
+      <c r="E312" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F312" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G312" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H312" s="8" t="inlineStr">
+        <is>
+          <t>(423) 843-3391</t>
+        </is>
+      </c>
+      <c r="I312" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J312" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K312" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L312" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M312" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N312" s="8" t="inlineStr">
+        <is>
+          <t>Established electrical contractor with review history; likely multi-van fleet</t>
+        </is>
+      </c>
+      <c r="O312" s="8" t="inlineStr">
+        <is>
+          <t>BuildZoom contractor profile</t>
+        </is>
+      </c>
+      <c r="P312" s="8" t="inlineStr">
+        <is>
+          <t>BuildZoom profile</t>
+        </is>
+      </c>
+      <c r="Q312" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R312" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="8" t="inlineStr">
+        <is>
+          <t>Physicians Care Walk-in Clinic - Hixson</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>Urgent Care / Medical</t>
+        </is>
+      </c>
+      <c r="C313" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>4490 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F313" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G313" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>(423) 875-0700</t>
+        </is>
+      </c>
+      <c r="I313" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J313" s="8" t="inlineStr">
+        <is>
+          <t>urgentteam.com</t>
+        </is>
+      </c>
+      <c r="K313" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L313" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M313" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N313" s="8" t="inlineStr">
+        <is>
+          <t>Regional urgent-care chain location; local referral-network prospect</t>
+        </is>
+      </c>
+      <c r="O313" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing (23 reviews)</t>
+        </is>
+      </c>
+      <c r="P313" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q313" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R313" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="8" t="inlineStr">
+        <is>
+          <t>Hixson Elementary School</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="inlineStr">
+        <is>
+          <t>Public School (Hamilton County Schools)</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="inlineStr">
+        <is>
+          <t>5950 Winding Ln</t>
+        </is>
+      </c>
+      <c r="E314" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F314" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G314" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H314" s="8" t="inlineStr">
+        <is>
+          <t>(423) 870-0621</t>
+        </is>
+      </c>
+      <c r="I314" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J314" s="8" t="inlineStr">
+        <is>
+          <t>hes.hcde.org</t>
+        </is>
+      </c>
+      <c r="K314" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L314" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M314" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N314" s="8" t="inlineStr">
+        <is>
+          <t>School bus fleet operates daily on district routes</t>
+        </is>
+      </c>
+      <c r="O314" s="8" t="inlineStr">
+        <is>
+          <t>Active school website</t>
+        </is>
+      </c>
+      <c r="P314" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q314" s="8" t="inlineStr">
+        <is>
+          <t>NCES school directory</t>
+        </is>
+      </c>
+      <c r="R314" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>Hawaiian Bros</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant / Delivery</t>
+        </is>
+      </c>
+      <c r="C315" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>5118 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>(423) 471-4811</t>
+        </is>
+      </c>
+      <c r="I315" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J315" s="8" t="inlineStr">
+        <is>
+          <t>hawaiianbros.com</t>
+        </is>
+      </c>
+      <c r="K315" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L315" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M315" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N315" s="8" t="inlineStr">
+        <is>
+          <t>In-house delivery and catering vehicles on daily routes</t>
+        </is>
+      </c>
+      <c r="O315" s="8" t="inlineStr">
+        <is>
+          <t>Active location page</t>
+        </is>
+      </c>
+      <c r="P315" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q315" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R315" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="8" t="inlineStr">
+        <is>
+          <t>Chicken Salad Chick - Hixson</t>
+        </is>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant / Catering</t>
+        </is>
+      </c>
+      <c r="C316" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D316" s="8" t="inlineStr">
+        <is>
+          <t>5100 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E316" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F316" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G316" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H316" s="8" t="inlineStr">
+        <is>
+          <t>(423) 668-0098</t>
+        </is>
+      </c>
+      <c r="I316" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J316" s="8" t="inlineStr">
+        <is>
+          <t>chickensaladchick.com</t>
+        </is>
+      </c>
+      <c r="K316" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L316" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M316" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N316" s="8" t="inlineStr">
+        <is>
+          <t>Catering delivery vehicles on daily local routes</t>
+        </is>
+      </c>
+      <c r="O316" s="8" t="inlineStr">
+        <is>
+          <t>Active location page</t>
+        </is>
+      </c>
+      <c r="P316" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q316" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R316" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>Bibas Italian Restaurant</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant / Catering</t>
+        </is>
+      </c>
+      <c r="C317" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>5918 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>Hixson</t>
+        </is>
+      </c>
+      <c r="F317" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G317" s="8" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>(423) 843-0001</t>
+        </is>
+      </c>
+      <c r="I317" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J317" s="8" t="inlineStr">
+        <is>
+          <t>italianrestauranthixson.com</t>
+        </is>
+      </c>
+      <c r="K317" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L317" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M317" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N317" s="8" t="inlineStr">
+        <is>
+          <t>Catering vehicle(s) for off-site events</t>
+        </is>
+      </c>
+      <c r="O317" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="P317" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q317" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages / local directory</t>
+        </is>
+      </c>
+      <c r="R317" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="8" t="inlineStr">
+        <is>
+          <t>Integrity Service Heating &amp; Cooling LLC</t>
+        </is>
+      </c>
+      <c r="B318" s="8" t="inlineStr">
+        <is>
+          <t>HVAC Contractor</t>
+        </is>
+      </c>
+      <c r="C318" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D318" s="8" t="inlineStr">
+        <is>
+          <t>106 Karen Dr</t>
+        </is>
+      </c>
+      <c r="E318" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F318" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G318" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H318" s="8" t="inlineStr">
+        <is>
+          <t>(423) 356-8282</t>
+        </is>
+      </c>
+      <c r="I318" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J318" s="8" t="inlineStr">
+        <is>
+          <t>integrityheatandcool.com</t>
+        </is>
+      </c>
+      <c r="K318" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L318" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M318" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N318" s="8" t="inlineStr">
+        <is>
+          <t>Service trucks in the field daily for HVAC calls; high windshield-chip exposure</t>
+        </is>
+      </c>
+      <c r="O318" s="8" t="inlineStr">
+        <is>
+          <t>Active website with service booking</t>
+        </is>
+      </c>
+      <c r="P318" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q318" s="8" t="inlineStr">
+        <is>
+          <t>HVAC directory listing</t>
+        </is>
+      </c>
+      <c r="R318" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="8" t="inlineStr">
+        <is>
+          <t>Soddy Daisy MountainView Heating &amp; Cooling</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>HVAC Contractor</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>122 Harrison Ln</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G319" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H319" s="8" t="inlineStr">
+        <is>
+          <t>(423) 520-8099</t>
+        </is>
+      </c>
+      <c r="I319" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J319" s="8" t="inlineStr">
+        <is>
+          <t>soddydaisymountainviewheatingcooling.com</t>
+        </is>
+      </c>
+      <c r="K319" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L319" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M319" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N319" s="8" t="inlineStr">
+        <is>
+          <t>Local HVAC dispatch fleet with a same-day service model similar to prospect's own</t>
+        </is>
+      </c>
+      <c r="O319" s="8" t="inlineStr">
+        <is>
+          <t>Active service website</t>
+        </is>
+      </c>
+      <c r="P319" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q319" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="R319" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="8" t="inlineStr">
+        <is>
+          <t>All Around Heating and Air</t>
+        </is>
+      </c>
+      <c r="B320" s="8" t="inlineStr">
+        <is>
+          <t>HVAC Contractor</t>
+        </is>
+      </c>
+      <c r="C320" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D320" s="8" t="inlineStr">
+        <is>
+          <t>1000 Falcon Run Dr</t>
+        </is>
+      </c>
+      <c r="E320" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F320" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G320" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H320" s="8" t="inlineStr">
+        <is>
+          <t>(423) 760-1273</t>
+        </is>
+      </c>
+      <c r="I320" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J320" s="8" t="inlineStr">
+        <is>
+          <t>aaheatingandairtn.com</t>
+        </is>
+      </c>
+      <c r="K320" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L320" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M320" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N320" s="8" t="inlineStr">
+        <is>
+          <t>Residential/commercial HVAC service vehicles running daily routes</t>
+        </is>
+      </c>
+      <c r="O320" s="8" t="inlineStr">
+        <is>
+          <t>Active website with service area pages</t>
+        </is>
+      </c>
+      <c r="P320" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q320" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R320" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="8" t="inlineStr">
+        <is>
+          <t>Elite Heating &amp; Air</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>HVAC Contractor</t>
+        </is>
+      </c>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>12816 Old Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F321" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G321" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H321" s="8" t="inlineStr">
+        <is>
+          <t>(423) 451-2001</t>
+        </is>
+      </c>
+      <c r="I321" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J321" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K321" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L321" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M321" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N321" s="8" t="inlineStr">
+        <is>
+          <t>Field-service HVAC company likely running a multi-van fleet</t>
+        </is>
+      </c>
+      <c r="O321" s="8" t="inlineStr">
+        <is>
+          <t>Active chamber directory listing</t>
+        </is>
+      </c>
+      <c r="P321" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="Q321" s="8" t="inlineStr">
+        <is>
+          <t>BBB category page</t>
+        </is>
+      </c>
+      <c r="R321" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="8" t="inlineStr">
+        <is>
+          <t>Allied Electrical &amp; Control</t>
+        </is>
+      </c>
+      <c r="B322" s="8" t="inlineStr">
+        <is>
+          <t>Electrical Contractor</t>
+        </is>
+      </c>
+      <c r="C322" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D322" s="8" t="inlineStr">
+        <is>
+          <t>8800 Consolidated Dr</t>
+        </is>
+      </c>
+      <c r="E322" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F322" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G322" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H322" s="8" t="inlineStr">
+        <is>
+          <t>(423) 877-7421</t>
+        </is>
+      </c>
+      <c r="I322" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J322" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K322" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L322" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M322" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N322" s="8" t="inlineStr">
+        <is>
+          <t>Commercial/industrial electrical contractor with service trucks</t>
+        </is>
+      </c>
+      <c r="O322" s="8" t="inlineStr">
+        <is>
+          <t>BBB business profile</t>
+        </is>
+      </c>
+      <c r="P322" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q322" s="8" t="inlineStr">
+        <is>
+          <t>Manta.com listing</t>
+        </is>
+      </c>
+      <c r="R322" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="8" t="inlineStr">
+        <is>
+          <t>Cordell's Electric</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr">
+        <is>
+          <t>Electrical Contractor</t>
+        </is>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>104 Thrasher Pike</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G323" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H323" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-0676</t>
+        </is>
+      </c>
+      <c r="I323" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J323" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K323" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L323" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M323" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N323" s="8" t="inlineStr">
+        <is>
+          <t>Residential/commercial electrician with a likely service van fleet</t>
+        </is>
+      </c>
+      <c r="O323" s="8" t="inlineStr">
+        <is>
+          <t>Active Nextdoor business page</t>
+        </is>
+      </c>
+      <c r="P323" s="8" t="inlineStr">
+        <is>
+          <t>Nextdoor business page</t>
+        </is>
+      </c>
+      <c r="Q323" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R323" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="8" t="inlineStr">
+        <is>
+          <t>Crider Landscaping</t>
+        </is>
+      </c>
+      <c r="B324" s="8" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="C324" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D324" s="8" t="inlineStr">
+        <is>
+          <t>1645 Wendy Circle</t>
+        </is>
+      </c>
+      <c r="E324" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F324" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G324" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H324" s="8" t="inlineStr">
+        <is>
+          <t>(423) 708-5646</t>
+        </is>
+      </c>
+      <c r="I324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N324" s="8" t="inlineStr">
+        <is>
+          <t>Landscaping crews run trucks/trailers on rough terrain; high glass-damage rate</t>
+        </is>
+      </c>
+      <c r="O324" s="8" t="inlineStr">
+        <is>
+          <t>Listed on Yellow Pages with reviews</t>
+        </is>
+      </c>
+      <c r="P324" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="Q324" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R324" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="8" t="inlineStr">
+        <is>
+          <t>Nooga Lawn and Landscaping</t>
+        </is>
+      </c>
+      <c r="B325" s="8" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D325" s="8" t="inlineStr">
+        <is>
+          <t>8414 Gulf View Dr</t>
+        </is>
+      </c>
+      <c r="E325" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F325" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G325" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H325" s="8" t="inlineStr">
+        <is>
+          <t>(423) 637-6874</t>
+        </is>
+      </c>
+      <c r="I325" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J325" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K325" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L325" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M325" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N325" s="8" t="inlineStr">
+        <is>
+          <t>Landscape crew trucks/trailers with rock and debris exposure to windshields</t>
+        </is>
+      </c>
+      <c r="O325" s="8" t="inlineStr">
+        <is>
+          <t>Active Birdeye reviews profile</t>
+        </is>
+      </c>
+      <c r="P325" s="8" t="inlineStr">
+        <is>
+          <t>Birdeye reviews</t>
+        </is>
+      </c>
+      <c r="Q325" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="R325" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="8" t="inlineStr">
+        <is>
+          <t>L H Lewis Tree Service</t>
+        </is>
+      </c>
+      <c r="B326" s="8" t="inlineStr">
+        <is>
+          <t>Tree Service</t>
+        </is>
+      </c>
+      <c r="C326" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D326" s="8" t="inlineStr">
+        <is>
+          <t>8307 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E326" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F326" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G326" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H326" s="8" t="inlineStr">
+        <is>
+          <t>(423) 843-3593</t>
+        </is>
+      </c>
+      <c r="I326" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J326" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K326" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L326" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M326" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N326" s="8" t="inlineStr">
+        <is>
+          <t>33 years in business; tree/chipper trucks highly prone to windshield damage</t>
+        </is>
+      </c>
+      <c r="O326" s="8" t="inlineStr">
+        <is>
+          <t>Long operating history cited</t>
+        </is>
+      </c>
+      <c r="P326" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="Q326" s="8" t="inlineStr">
+        <is>
+          <t>Manta.com listing</t>
+        </is>
+      </c>
+      <c r="R326" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="8" t="inlineStr">
+        <is>
+          <t>S &amp; H Tree Service</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Tree Service</t>
+        </is>
+      </c>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D327" s="8" t="inlineStr">
+        <is>
+          <t>208 Daisy Ave</t>
+        </is>
+      </c>
+      <c r="E327" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F327" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G327" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H327" s="8" t="inlineStr">
+        <is>
+          <t>(423) 451-0437</t>
+        </is>
+      </c>
+      <c r="I327" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J327" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K327" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L327" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M327" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N327" s="8" t="inlineStr">
+        <is>
+          <t>Tree removal/chipping trucks with very high rock-strike/glass-damage risk</t>
+        </is>
+      </c>
+      <c r="O327" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp business listing</t>
+        </is>
+      </c>
+      <c r="P327" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q327" s="8" t="inlineStr">
+        <is>
+          <t>homeyou.com listing</t>
+        </is>
+      </c>
+      <c r="R327" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="8" t="inlineStr">
+        <is>
+          <t>Manzano Masonry</t>
+        </is>
+      </c>
+      <c r="B328" s="8" t="inlineStr">
+        <is>
+          <t>Masonry / Concrete</t>
+        </is>
+      </c>
+      <c r="C328" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D328" s="8" t="inlineStr">
+        <is>
+          <t>124 Harrison Ln</t>
+        </is>
+      </c>
+      <c r="E328" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F328" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G328" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H328" s="8" t="inlineStr">
+        <is>
+          <t>(423) 298-8859</t>
+        </is>
+      </c>
+      <c r="I328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N328" s="8" t="inlineStr">
+        <is>
+          <t>Masonry trucks hauling stone/block material; frequent rock-chip exposure</t>
+        </is>
+      </c>
+      <c r="O328" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with 41 photos, active reviews</t>
+        </is>
+      </c>
+      <c r="P328" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q328" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R328" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="8" t="inlineStr">
+        <is>
+          <t>Nooga Door Company</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t>Garage Door Installation / Repair</t>
+        </is>
+      </c>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D329" s="8" t="inlineStr">
+        <is>
+          <t>8857 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E329" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F329" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G329" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H329" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-5098</t>
+        </is>
+      </c>
+      <c r="I329" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J329" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K329" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L329" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M329" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N329" s="8" t="inlineStr">
+        <is>
+          <t>Install/repair techs drive daily routes carrying door panels and parts</t>
+        </is>
+      </c>
+      <c r="O329" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with 15 photos</t>
+        </is>
+      </c>
+      <c r="P329" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q329" s="8" t="inlineStr">
+        <is>
+          <t>pr.business listing</t>
+        </is>
+      </c>
+      <c r="R329" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="8" t="inlineStr">
+        <is>
+          <t>Hazelwood Painting</t>
+        </is>
+      </c>
+      <c r="B330" s="8" t="inlineStr">
+        <is>
+          <t>Painting Contractor</t>
+        </is>
+      </c>
+      <c r="C330" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D330" s="8" t="inlineStr">
+        <is>
+          <t>1235 Thatcher Rd</t>
+        </is>
+      </c>
+      <c r="E330" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F330" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G330" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H330" s="8" t="inlineStr">
+        <is>
+          <t>(423) 802-1379</t>
+        </is>
+      </c>
+      <c r="I330" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J330" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K330" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L330" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M330" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N330" s="8" t="inlineStr">
+        <is>
+          <t>Crew trucks/trailers running job sites daily</t>
+        </is>
+      </c>
+      <c r="O330" s="8" t="inlineStr">
+        <is>
+          <t>Listed on BBB Soddy-Daisy painting category</t>
+        </is>
+      </c>
+      <c r="P330" s="8" t="inlineStr">
+        <is>
+          <t>BBB category page</t>
+        </is>
+      </c>
+      <c r="Q330" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R330" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="8" t="inlineStr">
+        <is>
+          <t>Chattanooga Professional Painters</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr">
+        <is>
+          <t>Painting Contractor</t>
+        </is>
+      </c>
+      <c r="C331" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D331" s="8" t="inlineStr">
+        <is>
+          <t>8006 Freeport Dr</t>
+        </is>
+      </c>
+      <c r="E331" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F331" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G331" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H331" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-3008</t>
+        </is>
+      </c>
+      <c r="I331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N331" s="8" t="inlineStr">
+        <is>
+          <t>Commercial/residential painting crew fleet</t>
+        </is>
+      </c>
+      <c r="O331" s="8" t="inlineStr">
+        <is>
+          <t>Active directory listing</t>
+        </is>
+      </c>
+      <c r="P331" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="Q331" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R331" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="8" t="inlineStr">
+        <is>
+          <t>Wilkey Roofing</t>
+        </is>
+      </c>
+      <c r="B332" s="8" t="inlineStr">
+        <is>
+          <t>Roofing Contractor</t>
+        </is>
+      </c>
+      <c r="C332" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D332" s="8" t="inlineStr">
+        <is>
+          <t>317 Walnut Cir</t>
+        </is>
+      </c>
+      <c r="E332" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F332" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G332" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H332" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-6710</t>
+        </is>
+      </c>
+      <c r="I332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N332" s="8" t="inlineStr">
+        <is>
+          <t>Roofing crews haul ladders/material trucks over debris-strewn job sites</t>
+        </is>
+      </c>
+      <c r="O332" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp business listing</t>
+        </is>
+      </c>
+      <c r="P332" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q332" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R332" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="8" t="inlineStr">
+        <is>
+          <t>Petra Roofing &amp; Siding</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr">
+        <is>
+          <t>Roofing / Siding Contractor</t>
+        </is>
+      </c>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="inlineStr">
+        <is>
+          <t>10903 Daffodil Cir</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F333" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G333" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H333" s="8" t="inlineStr">
+        <is>
+          <t>(423) 593-1816</t>
+        </is>
+      </c>
+      <c r="I333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N333" s="8" t="inlineStr">
+        <is>
+          <t>Roofing/siding crew trucks with high rock-chip exposure</t>
+        </is>
+      </c>
+      <c r="O333" s="8" t="inlineStr">
+        <is>
+          <t>Listed in TheBlueBook ProView contractor directory</t>
+        </is>
+      </c>
+      <c r="P333" s="8" t="inlineStr">
+        <is>
+          <t>TheBlueBook listing</t>
+        </is>
+      </c>
+      <c r="Q333" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R333" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="8" t="inlineStr">
+        <is>
+          <t>Harbor Lights Marina</t>
+        </is>
+      </c>
+      <c r="B334" s="8" t="inlineStr">
+        <is>
+          <t>Marina / Boat Services</t>
+        </is>
+      </c>
+      <c r="C334" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D334" s="8" t="inlineStr">
+        <is>
+          <t>9680 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E334" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F334" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G334" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H334" s="8" t="inlineStr">
+        <is>
+          <t>(423) 842-5391</t>
+        </is>
+      </c>
+      <c r="I334" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J334" s="8" t="inlineStr">
+        <is>
+          <t>harborlightsmarinatn.com</t>
+        </is>
+      </c>
+      <c r="K334" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L334" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M334" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N334" s="8" t="inlineStr">
+        <is>
+          <t>Full-service marina with fuel dock, rental fleet, and staff/service trucks on Chickamauga Lake</t>
+        </is>
+      </c>
+      <c r="O334" s="8" t="inlineStr">
+        <is>
+          <t>Active website; Facebook page; Carefree Boat Club partner</t>
+        </is>
+      </c>
+      <c r="P334" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q334" s="8" t="inlineStr">
+        <is>
+          <t>Facebook page</t>
+        </is>
+      </c>
+      <c r="R334" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="8" t="inlineStr">
+        <is>
+          <t>Daisy Feed &amp; Seed Company</t>
+        </is>
+      </c>
+      <c r="B335" s="8" t="inlineStr">
+        <is>
+          <t>Agricultural Supply / Garden Center</t>
+        </is>
+      </c>
+      <c r="C335" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D335" s="8" t="inlineStr">
+        <is>
+          <t>9554 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E335" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F335" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G335" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H335" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-2481</t>
+        </is>
+      </c>
+      <c r="I335" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J335" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K335" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L335" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M335" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N335" s="8" t="inlineStr">
+        <is>
+          <t>Feed/seed store likely running delivery trucks for bulk agricultural products</t>
+        </is>
+      </c>
+      <c r="O335" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P335" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q335" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R335" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="8" t="inlineStr">
+        <is>
+          <t>Tractor Supply Co. #176</t>
+        </is>
+      </c>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t>Farm / Ranch Retail</t>
+        </is>
+      </c>
+      <c r="C336" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D336" s="8" t="inlineStr">
+        <is>
+          <t>222 Sequoyah Rd</t>
+        </is>
+      </c>
+      <c r="E336" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F336" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G336" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H336" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-5434</t>
+        </is>
+      </c>
+      <c r="I336" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J336" s="8" t="inlineStr">
+        <is>
+          <t>tractorsupply.com</t>
+        </is>
+      </c>
+      <c r="K336" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L336" s="8" t="inlineStr">
+        <is>
+          <t>Store Manager (name not published)</t>
+        </is>
+      </c>
+      <c r="M336" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N336" s="8" t="inlineStr">
+        <is>
+          <t>National chain store with local delivery/curbside fleet vehicles</t>
+        </is>
+      </c>
+      <c r="O336" s="8" t="inlineStr">
+        <is>
+          <t>Official Tractor Supply store locator page</t>
+        </is>
+      </c>
+      <c r="P336" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q336" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R336" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="8" t="inlineStr">
+        <is>
+          <t>R&amp;A Catering</t>
+        </is>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="C337" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D337" s="8" t="inlineStr">
+        <is>
+          <t>1983 Breeze Dr</t>
+        </is>
+      </c>
+      <c r="E337" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F337" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G337" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H337" s="8" t="inlineStr">
+        <is>
+          <t>(423) 598-8855</t>
+        </is>
+      </c>
+      <c r="I337" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J337" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K337" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L337" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M337" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N337" s="8" t="inlineStr">
+        <is>
+          <t>Catering vans making frequent delivery runs</t>
+        </is>
+      </c>
+      <c r="O337" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing with 29 photos</t>
+        </is>
+      </c>
+      <c r="P337" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q337" s="8" t="inlineStr">
+        <is>
+          <t>Nextdoor business page</t>
+        </is>
+      </c>
+      <c r="R337" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="8" t="inlineStr">
+        <is>
+          <t>Shuford's Smokehouse</t>
+        </is>
+      </c>
+      <c r="B338" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant / BBQ with Catering</t>
+        </is>
+      </c>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D338" s="8" t="inlineStr">
+        <is>
+          <t>11320 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E338" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F338" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G338" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H338" s="8" t="inlineStr">
+        <is>
+          <t>(423) 451-7102</t>
+        </is>
+      </c>
+      <c r="I338" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J338" s="8" t="inlineStr">
+        <is>
+          <t>roostcafeandbistro.com/shufords-smokehouse-soddy-daisy-37379</t>
+        </is>
+      </c>
+      <c r="K338" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L338" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M338" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N338" s="8" t="inlineStr">
+        <is>
+          <t>Smokehouse/catering operation likely running a delivery/catering vehicle</t>
+        </is>
+      </c>
+      <c r="O338" s="8" t="inlineStr">
+        <is>
+          <t>Listed on affiliated restaurant group site</t>
+        </is>
+      </c>
+      <c r="P338" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q338" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R338" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="8" t="inlineStr">
+        <is>
+          <t>Soddy Daisy Speed Shop and Auto Repair, LLC</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C339" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D339" s="8" t="inlineStr">
+        <is>
+          <t>9632 Dayton Pike #102</t>
+        </is>
+      </c>
+      <c r="E339" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F339" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G339" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H339" s="8" t="inlineStr">
+        <is>
+          <t>(423) 667-8560</t>
+        </is>
+      </c>
+      <c r="I339" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J339" s="8" t="inlineStr">
+        <is>
+          <t>soddyspeed.com</t>
+        </is>
+      </c>
+      <c r="K339" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L339" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M339" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N339" s="8" t="inlineStr">
+        <is>
+          <t>Auto shop with shuttle/loaner and shop vehicles; also referral-partner potential</t>
+        </is>
+      </c>
+      <c r="O339" s="8" t="inlineStr">
+        <is>
+          <t>81 reviews on autorepairscore.com</t>
+        </is>
+      </c>
+      <c r="P339" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q339" s="8" t="inlineStr">
+        <is>
+          <t>autorepairscore.com listing</t>
+        </is>
+      </c>
+      <c r="R339" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="8" t="inlineStr">
+        <is>
+          <t>Andy's Automotive</t>
+        </is>
+      </c>
+      <c r="B340" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C340" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D340" s="8" t="inlineStr">
+        <is>
+          <t>8644 El Dee Ln</t>
+        </is>
+      </c>
+      <c r="E340" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F340" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G340" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H340" s="8" t="inlineStr">
+        <is>
+          <t>(423) 785-6189</t>
+        </is>
+      </c>
+      <c r="I340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N340" s="8" t="inlineStr">
+        <is>
+          <t>Auto shop with shop/loaner vehicles; potential referral partner for glass work</t>
+        </is>
+      </c>
+      <c r="O340" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P340" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q340" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R340" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="8" t="inlineStr">
+        <is>
+          <t>ETN Cleaning Services</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Commercial / Residential Cleaning</t>
+        </is>
+      </c>
+      <c r="C341" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D341" s="8" t="inlineStr">
+        <is>
+          <t>8890 Hunt St STE 200</t>
+        </is>
+      </c>
+      <c r="E341" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F341" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G341" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H341" s="8" t="inlineStr">
+        <is>
+          <t>(423) 883-7978</t>
+        </is>
+      </c>
+      <c r="I341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N341" s="8" t="inlineStr">
+        <is>
+          <t>Cleaning crews driving multiple routes daily across Hamilton County</t>
+        </is>
+      </c>
+      <c r="O341" s="8" t="inlineStr">
+        <is>
+          <t>BBB A-rating profile</t>
+        </is>
+      </c>
+      <c r="P341" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q341" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R341" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="8" t="inlineStr">
+        <is>
+          <t>First Presbyterian Church (Soddy-Daisy)</t>
+        </is>
+      </c>
+      <c r="B342" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C342" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D342" s="8" t="inlineStr">
+        <is>
+          <t>10612 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E342" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F342" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G342" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H342" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-2327</t>
+        </is>
+      </c>
+      <c r="I342" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J342" s="8" t="inlineStr">
+        <is>
+          <t>pcusa.org/congregation/first-church-soddy-daisy-tn</t>
+        </is>
+      </c>
+      <c r="K342" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L342" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M342" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N342" s="8" t="inlineStr">
+        <is>
+          <t>Congregation likely operates outreach/shuttle vans</t>
+        </is>
+      </c>
+      <c r="O342" s="8" t="inlineStr">
+        <is>
+          <t>Listed on PCUSA national denomination directory</t>
+        </is>
+      </c>
+      <c r="P342" s="8" t="inlineStr">
+        <is>
+          <t>PCUSA directory</t>
+        </is>
+      </c>
+      <c r="Q342" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R342" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="8" t="inlineStr">
+        <is>
+          <t>Daisy Church of God</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C343" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>9555 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F343" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G343" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H343" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-2558</t>
+        </is>
+      </c>
+      <c r="I343" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J343" s="8" t="inlineStr">
+        <is>
+          <t>daisychurchofgod.net</t>
+        </is>
+      </c>
+      <c r="K343" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L343" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M343" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N343" s="8" t="inlineStr">
+        <is>
+          <t>Church van/bus fleet potential for member transport</t>
+        </is>
+      </c>
+      <c r="O343" s="8" t="inlineStr">
+        <is>
+          <t>Active church website</t>
+        </is>
+      </c>
+      <c r="P343" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q343" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R343" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="8" t="inlineStr">
+        <is>
+          <t>Soddy Church of Christ</t>
+        </is>
+      </c>
+      <c r="B344" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C344" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D344" s="8" t="inlineStr">
+        <is>
+          <t>11665 Hixson Pike</t>
+        </is>
+      </c>
+      <c r="E344" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F344" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G344" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H344" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-1418</t>
+        </is>
+      </c>
+      <c r="I344" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J344" s="8" t="inlineStr">
+        <is>
+          <t>soddychurchofchrist.org</t>
+        </is>
+      </c>
+      <c r="K344" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L344" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M344" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N344" s="8" t="inlineStr">
+        <is>
+          <t>Church van/bus fleet potential</t>
+        </is>
+      </c>
+      <c r="O344" s="8" t="inlineStr">
+        <is>
+          <t>Active church website</t>
+        </is>
+      </c>
+      <c r="P344" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q344" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R344" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="8" t="inlineStr">
+        <is>
+          <t>Holy Spirit Catholic Church</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C345" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>10768 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F345" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G345" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H345" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-5300</t>
+        </is>
+      </c>
+      <c r="I345" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J345" s="8" t="inlineStr">
+        <is>
+          <t>holyspiritsoddydaisy.com</t>
+        </is>
+      </c>
+      <c r="K345" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L345" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M345" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N345" s="8" t="inlineStr">
+        <is>
+          <t>Parish likely runs outreach/school-affiliated vehicles</t>
+        </is>
+      </c>
+      <c r="O345" s="8" t="inlineStr">
+        <is>
+          <t>Active parish website with contact page</t>
+        </is>
+      </c>
+      <c r="P345" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q345" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R345" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="8" t="inlineStr">
+        <is>
+          <t>Soddy Daisy First Baptist Church</t>
+        </is>
+      </c>
+      <c r="B346" s="8" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C346" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D346" s="8" t="inlineStr">
+        <is>
+          <t>10185 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E346" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F346" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G346" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H346" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-2814</t>
+        </is>
+      </c>
+      <c r="I346" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J346" s="8" t="inlineStr">
+        <is>
+          <t>fbcsoddydaisy.com</t>
+        </is>
+      </c>
+      <c r="K346" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L346" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M346" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N346" s="8" t="inlineStr">
+        <is>
+          <t>Large Baptist congregation; common to operate bus ministry</t>
+        </is>
+      </c>
+      <c r="O346" s="8" t="inlineStr">
+        <is>
+          <t>Active website with staff/service-times pages</t>
+        </is>
+      </c>
+      <c r="P346" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q346" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R346" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="8" t="inlineStr">
+        <is>
+          <t>Soddy Daisy Smiles (Drs. Mandy &amp; Robert Shearer)</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C347" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>9759 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G347" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H347" s="8" t="inlineStr">
+        <is>
+          <t>(423) 332-5275</t>
+        </is>
+      </c>
+      <c r="I347" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J347" s="8" t="inlineStr">
+        <is>
+          <t>soddydaisysmiles.com</t>
+        </is>
+      </c>
+      <c r="K347" s="8" t="inlineStr">
+        <is>
+          <t>Dr. Mandy Shearer / Dr. Robert Shearer</t>
+        </is>
+      </c>
+      <c r="L347" s="8" t="inlineStr">
+        <is>
+          <t>Dentists (Owners)</t>
+        </is>
+      </c>
+      <c r="M347" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N347" s="8" t="inlineStr">
+        <is>
+          <t>Low fleet need, but referral/networking value in the local business community</t>
+        </is>
+      </c>
+      <c r="O347" s="8" t="inlineStr">
+        <is>
+          <t>11 reviews on Yelp</t>
+        </is>
+      </c>
+      <c r="P347" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q347" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R347" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="8" t="inlineStr">
+        <is>
+          <t>Northpoint Dental Company</t>
+        </is>
+      </c>
+      <c r="B348" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D348" s="8" t="inlineStr">
+        <is>
+          <t>124 Harrison Lane, Suite 100</t>
+        </is>
+      </c>
+      <c r="E348" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F348" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G348" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H348" s="8" t="inlineStr">
+        <is>
+          <t>(423) 454-1935</t>
+        </is>
+      </c>
+      <c r="I348" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J348" s="8" t="inlineStr">
+        <is>
+          <t>northpointdentalco.com</t>
+        </is>
+      </c>
+      <c r="K348" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L348" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M348" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N348" s="8" t="inlineStr">
+        <is>
+          <t>Low fleet need, referral/networking value only</t>
+        </is>
+      </c>
+      <c r="O348" s="8" t="inlineStr">
+        <is>
+          <t>Active practice website with hours</t>
+        </is>
+      </c>
+      <c r="P348" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q348" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R348" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="8" t="inlineStr">
+        <is>
+          <t>Fast Pace Health Urgent Care (Soddy-Daisy)</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr">
+        <is>
+          <t>Urgent Care Clinic</t>
+        </is>
+      </c>
+      <c r="C349" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D349" s="8" t="inlineStr">
+        <is>
+          <t>9325 Dayton Pike</t>
+        </is>
+      </c>
+      <c r="E349" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F349" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G349" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H349" s="8" t="inlineStr">
+        <is>
+          <t>(423) 451-4018</t>
+        </is>
+      </c>
+      <c r="I349" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J349" s="8" t="inlineStr">
+        <is>
+          <t>fastpacehealth.com</t>
+        </is>
+      </c>
+      <c r="K349" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L349" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M349" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N349" s="8" t="inlineStr">
+        <is>
+          <t>Regional chain clinic; low direct fleet relevance but high foot traffic for referrals</t>
+        </is>
+      </c>
+      <c r="O349" s="8" t="inlineStr">
+        <is>
+          <t>1,228 reviews on Birdeye</t>
+        </is>
+      </c>
+      <c r="P349" s="8" t="inlineStr">
+        <is>
+          <t>Birdeye reviews</t>
+        </is>
+      </c>
+      <c r="Q349" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R349" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="8" t="inlineStr">
+        <is>
+          <t>Sto A Way Storage (U-Haul Neighborhood Dealer)</t>
+        </is>
+      </c>
+      <c r="B350" s="8" t="inlineStr">
+        <is>
+          <t>Self-Storage / Truck Rental</t>
+        </is>
+      </c>
+      <c r="C350" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D350" s="8" t="inlineStr">
+        <is>
+          <t>136 Bean St, Unit A</t>
+        </is>
+      </c>
+      <c r="E350" s="8" t="inlineStr">
+        <is>
+          <t>Soddy-Daisy</t>
+        </is>
+      </c>
+      <c r="F350" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G350" s="8" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="H350" s="8" t="inlineStr">
+        <is>
+          <t>(423) 243-3067</t>
+        </is>
+      </c>
+      <c r="I350" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J350" s="8" t="inlineStr">
+        <is>
+          <t>uhaul.com/Locations/Truck-Rentals-near-Soddy-Daisy-TN-37379/029022/</t>
+        </is>
+      </c>
+      <c r="K350" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L350" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M350" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N350" s="8" t="inlineStr">
+        <is>
+          <t>Rental truck fleet on-site; possible partnership for windshield service on rental units</t>
+        </is>
+      </c>
+      <c r="O350" s="8" t="inlineStr">
+        <is>
+          <t>Official U-Haul location page</t>
+        </is>
+      </c>
+      <c r="P350" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q350" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R350" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Exxon</t>
+        </is>
+      </c>
+      <c r="B351" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair / Towing / Gas Station</t>
+        </is>
+      </c>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D351" s="8" t="inlineStr">
+        <is>
+          <t>9416 Apison Pike</t>
+        </is>
+      </c>
+      <c r="E351" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F351" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G351" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H351" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-3863</t>
+        </is>
+      </c>
+      <c r="I351" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J351" s="8" t="inlineStr">
+        <is>
+          <t>collegedaleexxon.com</t>
+        </is>
+      </c>
+      <c r="K351" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L351" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M351" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N351" s="8" t="inlineStr">
+        <is>
+          <t>Auto repair/towing shop; natural referral partner for windshield damage found during service/inspections</t>
+        </is>
+      </c>
+      <c r="O351" s="8" t="inlineStr">
+        <is>
+          <t>Active site with service menu including towing; 14 Yelp reviews</t>
+        </is>
+      </c>
+      <c r="P351" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q351" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R351" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="8" t="inlineStr">
+        <is>
+          <t>Southern Auto Care</t>
+        </is>
+      </c>
+      <c r="B352" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C352" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D352" s="8" t="inlineStr">
+        <is>
+          <t>4961 Colcord Dr</t>
+        </is>
+      </c>
+      <c r="E352" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F352" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G352" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H352" s="8" t="inlineStr">
+        <is>
+          <t>(423) 719-4014</t>
+        </is>
+      </c>
+      <c r="I352" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J352" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K352" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L352" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M352" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N352" s="8" t="inlineStr">
+        <is>
+          <t>Independent repair shop with referral/partnership potential for windshield replacement overflow</t>
+        </is>
+      </c>
+      <c r="O352" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp/CARFAX listing with reviews and posted hours</t>
+        </is>
+      </c>
+      <c r="P352" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q352" s="8" t="inlineStr">
+        <is>
+          <t>CARFAX reviews page</t>
+        </is>
+      </c>
+      <c r="R352" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="8" t="inlineStr">
+        <is>
+          <t>Life Care Center of Collegedale</t>
+        </is>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
+          <t>Skilled Nursing / Rehab Facility</t>
+        </is>
+      </c>
+      <c r="C353" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D353" s="8" t="inlineStr">
+        <is>
+          <t>9210 Apison Pike</t>
+        </is>
+      </c>
+      <c r="E353" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F353" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G353" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H353" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-2182</t>
+        </is>
+      </c>
+      <c r="I353" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J353" s="8" t="inlineStr">
+        <is>
+          <t>lifecarecenterofcollegedale.com</t>
+        </is>
+      </c>
+      <c r="K353" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L353" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M353" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N353" s="8" t="inlineStr">
+        <is>
+          <t>124-bed facility likely operating resident transport van(s) exposed to lot damage and road debris</t>
+        </is>
+      </c>
+      <c r="O353" s="8" t="inlineStr">
+        <is>
+          <t>City of Collegedale official business directory</t>
+        </is>
+      </c>
+      <c r="P353" s="8" t="inlineStr">
+        <is>
+          <t>City business directory</t>
+        </is>
+      </c>
+      <c r="Q353" s="8" t="inlineStr">
+        <is>
+          <t>SeniorHousingNet facility listing</t>
+        </is>
+      </c>
+      <c r="R353" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="8" t="inlineStr">
+        <is>
+          <t>Southern Adventist University – Plant Services / Transportation</t>
+        </is>
+      </c>
+      <c r="B354" s="8" t="inlineStr">
+        <is>
+          <t>Higher Education – Facilities &amp; Fleet Operations</t>
+        </is>
+      </c>
+      <c r="C354" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D354" s="8" t="inlineStr">
+        <is>
+          <t>10101 Park Lane</t>
+        </is>
+      </c>
+      <c r="E354" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F354" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G354" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H354" s="8" t="inlineStr">
+        <is>
+          <t>(423) 236-2000</t>
+        </is>
+      </c>
+      <c r="I354" s="8" t="inlineStr">
+        <is>
+          <t>plantservice@southern.edu</t>
+        </is>
+      </c>
+      <c r="J354" s="8" t="inlineStr">
+        <is>
+          <t>southern.edu/administration/plant-services</t>
+        </is>
+      </c>
+      <c r="K354" s="8" t="inlineStr">
+        <is>
+          <t>Barry Becker</t>
+        </is>
+      </c>
+      <c r="L354" s="8" t="inlineStr">
+        <is>
+          <t>Transportation Services Director</t>
+        </is>
+      </c>
+      <c r="M354" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N354" s="8" t="inlineStr">
+        <is>
+          <t>University-owned maintenance trucks, grounds vehicles, and campus shuttles are constant candidates for windshield chips/cracks; large institutional buyer</t>
+        </is>
+      </c>
+      <c r="O354" s="8" t="inlineStr">
+        <is>
+          <t>Official Plant Services contact page</t>
+        </is>
+      </c>
+      <c r="P354" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q354" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce / Adventist Yearbook listing</t>
+        </is>
+      </c>
+      <c r="R354" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="8" t="inlineStr">
+        <is>
+          <t>Southern Adventist University – Dining Services</t>
+        </is>
+      </c>
+      <c r="B355" s="8" t="inlineStr">
+        <is>
+          <t>Higher Education – Food Service</t>
+        </is>
+      </c>
+      <c r="C355" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D355" s="8" t="inlineStr">
+        <is>
+          <t>4881 Taylor Circle</t>
+        </is>
+      </c>
+      <c r="E355" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F355" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G355" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H355" s="8" t="inlineStr">
+        <is>
+          <t>(423) 236-2708</t>
+        </is>
+      </c>
+      <c r="I355" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J355" s="8" t="inlineStr">
+        <is>
+          <t>southern.edu/food</t>
+        </is>
+      </c>
+      <c r="K355" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L355" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M355" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N355" s="8" t="inlineStr">
+        <is>
+          <t>Campus dining operations often run delivery/catering vehicles between kitchen and dining venues</t>
+        </is>
+      </c>
+      <c r="O355" s="8" t="inlineStr">
+        <is>
+          <t>Official food services contact page</t>
+        </is>
+      </c>
+      <c r="P355" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q355" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="R355" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Academy</t>
+        </is>
+      </c>
+      <c r="B356" s="8" t="inlineStr">
+        <is>
+          <t>K-12 Private School</t>
+        </is>
+      </c>
+      <c r="C356" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D356" s="8" t="inlineStr">
+        <is>
+          <t>4855 College Dr E</t>
+        </is>
+      </c>
+      <c r="E356" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F356" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G356" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H356" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-2124</t>
+        </is>
+      </c>
+      <c r="I356" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J356" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K356" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L356" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M356" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N356" s="8" t="inlineStr">
+        <is>
+          <t>K-12 school with a likely bus/van fleet for transport and athletics; gravel-route exposure</t>
+        </is>
+      </c>
+      <c r="O356" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp business listing</t>
+        </is>
+      </c>
+      <c r="P356" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q356" s="8" t="inlineStr">
+        <is>
+          <t>Chattanooga Area Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="R356" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="8" t="inlineStr">
+        <is>
+          <t>Kiddie Kampus</t>
+        </is>
+      </c>
+      <c r="B357" s="8" t="inlineStr">
+        <is>
+          <t>Child Care / Daycare</t>
+        </is>
+      </c>
+      <c r="C357" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D357" s="8" t="inlineStr">
+        <is>
+          <t>4829 College Dr E</t>
+        </is>
+      </c>
+      <c r="E357" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F357" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G357" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H357" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-9253</t>
+        </is>
+      </c>
+      <c r="I357" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J357" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K357" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L357" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M357" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N357" s="8" t="inlineStr">
+        <is>
+          <t>Long-running licensed daycare center likely running a van for field trips/pickup</t>
+        </is>
+      </c>
+      <c r="O357" s="8" t="inlineStr">
+        <is>
+          <t>Active listing with posted hours</t>
+        </is>
+      </c>
+      <c r="P357" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="Q357" s="8" t="inlineStr">
+        <is>
+          <t>Daycare directory listing</t>
+        </is>
+      </c>
+      <c r="R357" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="8" t="inlineStr">
+        <is>
+          <t>McKee Foods Bakery Store (Little Debbie Bakery Store)</t>
+        </is>
+      </c>
+      <c r="B358" s="8" t="inlineStr">
+        <is>
+          <t>Bakery Retail / Food Distribution</t>
+        </is>
+      </c>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D358" s="8" t="inlineStr">
+        <is>
+          <t>9515 Apison Pike</t>
+        </is>
+      </c>
+      <c r="E358" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F358" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G358" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H358" s="8" t="inlineStr">
+        <is>
+          <t>(423) 238-2205</t>
+        </is>
+      </c>
+      <c r="I358" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J358" s="8" t="inlineStr">
+        <is>
+          <t>mckeefoods.com/our-bakery-stores</t>
+        </is>
+      </c>
+      <c r="K358" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L358" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M358" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N358" s="8" t="inlineStr">
+        <is>
+          <t>Retail storefront tied to McKee Foods' local delivery/restocking activity</t>
+        </is>
+      </c>
+      <c r="O358" s="8" t="inlineStr">
+        <is>
+          <t>City of Collegedale official business directory</t>
+        </is>
+      </c>
+      <c r="P358" s="8" t="inlineStr">
+        <is>
+          <t>City business directory</t>
+        </is>
+      </c>
+      <c r="Q358" s="8" t="inlineStr">
+        <is>
+          <t>McKee Foods corporate bakery store list</t>
+        </is>
+      </c>
+      <c r="R358" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="8" t="inlineStr">
+        <is>
+          <t>Village Market</t>
+        </is>
+      </c>
+      <c r="B359" s="8" t="inlineStr">
+        <is>
+          <t>Grocery Store</t>
+        </is>
+      </c>
+      <c r="C359" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D359" s="8" t="inlineStr">
+        <is>
+          <t>5002 University Dr</t>
+        </is>
+      </c>
+      <c r="E359" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F359" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G359" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H359" s="8" t="inlineStr">
+        <is>
+          <t>(423) 236-2300</t>
+        </is>
+      </c>
+      <c r="I359" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J359" s="8" t="inlineStr">
+        <is>
+          <t>vmcollegedale.com</t>
+        </is>
+      </c>
+      <c r="K359" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L359" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M359" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N359" s="8" t="inlineStr">
+        <is>
+          <t>Community grocery serving SAU/Collegedale with potential stocking/delivery vehicle exposure</t>
+        </is>
+      </c>
+      <c r="O359" s="8" t="inlineStr">
+        <is>
+          <t>BBB business profile</t>
+        </is>
+      </c>
+      <c r="P359" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q359" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R359" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="8" t="inlineStr">
+        <is>
+          <t>College Press (CP Publishing LLC)</t>
+        </is>
+      </c>
+      <c r="B360" s="8" t="inlineStr">
+        <is>
+          <t>Commercial Printing / Publishing</t>
+        </is>
+      </c>
+      <c r="C360" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D360" s="8" t="inlineStr">
+        <is>
+          <t>4981 Colcord Dr</t>
+        </is>
+      </c>
+      <c r="E360" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F360" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G360" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H360" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-2164</t>
+        </is>
+      </c>
+      <c r="I360" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J360" s="8" t="inlineStr">
+        <is>
+          <t>cplitho.com</t>
+        </is>
+      </c>
+      <c r="K360" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L360" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M360" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N360" s="8" t="inlineStr">
+        <is>
+          <t>Commercial print/publishing operation likely running delivery vehicles for print jobs and packaging materials</t>
+        </is>
+      </c>
+      <c r="O360" s="8" t="inlineStr">
+        <is>
+          <t>BBB business profile</t>
+        </is>
+      </c>
+      <c r="P360" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q360" s="8" t="inlineStr">
+        <is>
+          <t>City of Collegedale business directory</t>
+        </is>
+      </c>
+      <c r="R360" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Quick Print</t>
+        </is>
+      </c>
+      <c r="B361" s="8" t="inlineStr">
+        <is>
+          <t>Print Shop</t>
+        </is>
+      </c>
+      <c r="C361" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D361" s="8" t="inlineStr">
+        <is>
+          <t>5010 University Dr</t>
+        </is>
+      </c>
+      <c r="E361" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F361" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G361" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H361" s="8" t="inlineStr">
+        <is>
+          <t>(423) 236-2861</t>
+        </is>
+      </c>
+      <c r="I361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N361" s="8" t="inlineStr">
+        <is>
+          <t>Small local print shop with limited but plausible delivery vehicle use</t>
+        </is>
+      </c>
+      <c r="O361" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="P361" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="Q361" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="R361" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="8" t="inlineStr">
+        <is>
+          <t>Solutions Pharmacy, Inc.</t>
+        </is>
+      </c>
+      <c r="B362" s="8" t="inlineStr">
+        <is>
+          <t>Compounding Pharmacy</t>
+        </is>
+      </c>
+      <c r="C362" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D362" s="8" t="inlineStr">
+        <is>
+          <t>5517 Little Debbie Pkwy</t>
+        </is>
+      </c>
+      <c r="E362" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F362" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G362" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H362" s="8" t="inlineStr">
+        <is>
+          <t>(423) 894-3222</t>
+        </is>
+      </c>
+      <c r="I362" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J362" s="8" t="inlineStr">
+        <is>
+          <t>solutionspharmacy.com</t>
+        </is>
+      </c>
+      <c r="K362" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L362" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M362" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N362" s="8" t="inlineStr">
+        <is>
+          <t>Specialty/compounding pharmacies often run local delivery routes</t>
+        </is>
+      </c>
+      <c r="O362" s="8" t="inlineStr">
+        <is>
+          <t>City of Collegedale official business directory</t>
+        </is>
+      </c>
+      <c r="P362" s="8" t="inlineStr">
+        <is>
+          <t>City business directory</t>
+        </is>
+      </c>
+      <c r="Q362" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R362" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Medical Center, PC (Dr. David Winters, DO)</t>
+        </is>
+      </c>
+      <c r="B363" s="8" t="inlineStr">
+        <is>
+          <t>Family Medicine Practice</t>
+        </is>
+      </c>
+      <c r="C363" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D363" s="8" t="inlineStr">
+        <is>
+          <t>9310 Apison Pike</t>
+        </is>
+      </c>
+      <c r="E363" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F363" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G363" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H363" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-2136</t>
+        </is>
+      </c>
+      <c r="I363" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J363" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K363" s="8" t="inlineStr">
+        <is>
+          <t>Dr. David R. Winters</t>
+        </is>
+      </c>
+      <c r="L363" s="8" t="inlineStr">
+        <is>
+          <t>Physician / Practice Owner</t>
+        </is>
+      </c>
+      <c r="M363" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N363" s="8" t="inlineStr">
+        <is>
+          <t>Established family practice with a low but plausible fleet need for a staff/courier vehicle</t>
+        </is>
+      </c>
+      <c r="O363" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P363" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q363" s="8" t="inlineStr">
+        <is>
+          <t>Wellness.com practice profile</t>
+        </is>
+      </c>
+      <c r="R363" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Credit Union</t>
+        </is>
+      </c>
+      <c r="B364" s="8" t="inlineStr">
+        <is>
+          <t>Credit Union / Financial Services</t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D364" s="8" t="inlineStr">
+        <is>
+          <t>5046 University Dr</t>
+        </is>
+      </c>
+      <c r="E364" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F364" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G364" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H364" s="8" t="inlineStr">
+        <is>
+          <t>(423) 396-2101</t>
+        </is>
+      </c>
+      <c r="I364" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J364" s="8" t="inlineStr">
+        <is>
+          <t>collegedale.org</t>
+        </is>
+      </c>
+      <c r="K364" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L364" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M364" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N364" s="8" t="inlineStr">
+        <is>
+          <t>Local financial institution with minimal but possible courier/ATM-service vehicle exposure</t>
+        </is>
+      </c>
+      <c r="O364" s="8" t="inlineStr">
+        <is>
+          <t>Official contact page</t>
+        </is>
+      </c>
+      <c r="P364" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q364" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R364" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="8" t="inlineStr">
+        <is>
+          <t>Joy Chiropractic Clinic</t>
+        </is>
+      </c>
+      <c r="B365" s="8" t="inlineStr">
+        <is>
+          <t>Chiropractic Practice</t>
+        </is>
+      </c>
+      <c r="C365" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D365" s="8" t="inlineStr">
+        <is>
+          <t>9413 Apison Pike, Suite 122</t>
+        </is>
+      </c>
+      <c r="E365" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F365" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G365" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H365" s="8" t="inlineStr">
+        <is>
+          <t>(423) 298-1488</t>
+        </is>
+      </c>
+      <c r="I365" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J365" s="8" t="inlineStr">
+        <is>
+          <t>drjoychiropractic.com</t>
+        </is>
+      </c>
+      <c r="K365" s="8" t="inlineStr">
+        <is>
+          <t>Dr. Joy-Lynn Norris</t>
+        </is>
+      </c>
+      <c r="L365" s="8" t="inlineStr">
+        <is>
+          <t>Owner / Chiropractor</t>
+        </is>
+      </c>
+      <c r="M365" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N365" s="8" t="inlineStr">
+        <is>
+          <t>Small practice with limited fleet exposure but a valid local business contact</t>
+        </is>
+      </c>
+      <c r="O365" s="8" t="inlineStr">
+        <is>
+          <t>BBB business profile</t>
+        </is>
+      </c>
+      <c r="P365" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q365" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="R365" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale Coin Laundry</t>
+        </is>
+      </c>
+      <c r="B366" s="8" t="inlineStr">
+        <is>
+          <t>Laundromat</t>
+        </is>
+      </c>
+      <c r="C366" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D366" s="8" t="inlineStr">
+        <is>
+          <t>5032 Ooltewah-Ringgold Rd</t>
+        </is>
+      </c>
+      <c r="E366" s="8" t="inlineStr">
+        <is>
+          <t>Collegedale</t>
+        </is>
+      </c>
+      <c r="F366" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G366" s="8" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="H366" s="8" t="inlineStr">
+        <is>
+          <t>(423) 227-9926</t>
+        </is>
+      </c>
+      <c r="I366" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J366" s="8" t="inlineStr">
+        <is>
+          <t>collegedalecoinlaundry.com</t>
+        </is>
+      </c>
+      <c r="K366" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L366" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M366" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N366" s="8" t="inlineStr">
+        <is>
+          <t>Unattended coin laundry with no fleet expected but a valid local business contact</t>
+        </is>
+      </c>
+      <c r="O366" s="8" t="inlineStr">
+        <is>
+          <t>City of Collegedale official business directory</t>
+        </is>
+      </c>
+      <c r="P366" s="8" t="inlineStr">
+        <is>
+          <t>City business directory</t>
+        </is>
+      </c>
+      <c r="Q366" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R366" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="8" t="inlineStr">
+        <is>
+          <t>T.H.I. Electrical Contractors LLC</t>
+        </is>
+      </c>
+      <c r="B367" s="8" t="inlineStr">
+        <is>
+          <t>Electrical Contractor</t>
+        </is>
+      </c>
+      <c r="C367" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D367" s="8" t="inlineStr">
+        <is>
+          <t>950 Signal Rd</t>
+        </is>
+      </c>
+      <c r="E367" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F367" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G367" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H367" s="8" t="inlineStr">
+        <is>
+          <t>(423) 280-0251</t>
+        </is>
+      </c>
+      <c r="I367" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J367" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K367" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L367" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M367" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N367" s="8" t="inlineStr">
+        <is>
+          <t>Electrical contractors run daily service-truck routes on rough mountain roads; high windshield-chip/crack exposure</t>
+        </is>
+      </c>
+      <c r="O367" s="8" t="inlineStr">
+        <is>
+          <t>Active listing with reviews on Birdeye/Yelp</t>
+        </is>
+      </c>
+      <c r="P367" s="8" t="inlineStr">
+        <is>
+          <t>BBB electrician category</t>
+        </is>
+      </c>
+      <c r="Q367" s="8" t="inlineStr">
+        <is>
+          <t>Bizapedia LLC registration</t>
+        </is>
+      </c>
+      <c r="R367" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="8" t="inlineStr">
+        <is>
+          <t>Mountain City Service, Inc. (HVAC &amp; Plumbing)</t>
+        </is>
+      </c>
+      <c r="B368" s="8" t="inlineStr">
+        <is>
+          <t>HVAC / Plumbing Contractor</t>
+        </is>
+      </c>
+      <c r="C368" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D368" s="8" t="inlineStr">
+        <is>
+          <t>2408 Taft Hwy</t>
+        </is>
+      </c>
+      <c r="E368" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F368" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G368" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H368" s="8" t="inlineStr">
+        <is>
+          <t>(423) 801-1016</t>
+        </is>
+      </c>
+      <c r="I368" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J368" s="8" t="inlineStr">
+        <is>
+          <t>facebook.com/MountainCityService</t>
+        </is>
+      </c>
+      <c r="K368" s="8" t="inlineStr">
+        <is>
+          <t>Johnnie Rutledge / Eric Bryant</t>
+        </is>
+      </c>
+      <c r="L368" s="8" t="inlineStr">
+        <is>
+          <t>Owners</t>
+        </is>
+      </c>
+      <c r="M368" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N368" s="8" t="inlineStr">
+        <is>
+          <t>Multi-technician HVAC/plumbing outfit with daily dispatched trucks; BBB-accredited since 2015</t>
+        </is>
+      </c>
+      <c r="O368" s="8" t="inlineStr">
+        <is>
+          <t>BBB accredited profile; active Facebook page</t>
+        </is>
+      </c>
+      <c r="P368" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q368" s="8" t="inlineStr">
+        <is>
+          <t>Angi reviews listing</t>
+        </is>
+      </c>
+      <c r="R368" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="8" t="inlineStr">
+        <is>
+          <t>D &amp; G Roofing Specialists, LLC</t>
+        </is>
+      </c>
+      <c r="B369" s="8" t="inlineStr">
+        <is>
+          <t>Roofing Contractor</t>
+        </is>
+      </c>
+      <c r="C369" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D369" s="8" t="inlineStr">
+        <is>
+          <t>6850 Sawyer Rd</t>
+        </is>
+      </c>
+      <c r="E369" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F369" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G369" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H369" s="8" t="inlineStr">
+        <is>
+          <t>(423) 877-5716</t>
+        </is>
+      </c>
+      <c r="I369" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J369" s="8" t="inlineStr">
+        <is>
+          <t>dgroofingco.com</t>
+        </is>
+      </c>
+      <c r="K369" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L369" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M369" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N369" s="8" t="inlineStr">
+        <is>
+          <t>Roofing crews use multiple trucks/trailers for job sites; high exposure to debris/rock chips</t>
+        </is>
+      </c>
+      <c r="O369" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile; HBA of Greater Chattanooga member listing</t>
+        </is>
+      </c>
+      <c r="P369" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q369" s="8" t="inlineStr">
+        <is>
+          <t>HBA member directory</t>
+        </is>
+      </c>
+      <c r="R369" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="8" t="inlineStr">
+        <is>
+          <t>Signal Tree and Dirt Services</t>
+        </is>
+      </c>
+      <c r="B370" s="8" t="inlineStr">
+        <is>
+          <t>Tree Service</t>
+        </is>
+      </c>
+      <c r="C370" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D370" s="8" t="inlineStr">
+        <is>
+          <t>119 Short Creek Rd</t>
+        </is>
+      </c>
+      <c r="E370" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F370" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G370" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H370" s="8" t="inlineStr">
+        <is>
+          <t>(423) 413-2150</t>
+        </is>
+      </c>
+      <c r="I370" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J370" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K370" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L370" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M370" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N370" s="8" t="inlineStr">
+        <is>
+          <t>Tree service trucks/chippers operate on unpaved/wooded sites; very high windshield damage risk</t>
+        </is>
+      </c>
+      <c r="O370" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing with reviews</t>
+        </is>
+      </c>
+      <c r="P370" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q370" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R370" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain Nursery</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t>Landscaping / Nursery &amp; Garden Center</t>
+        </is>
+      </c>
+      <c r="C371" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D371" s="8" t="inlineStr">
+        <is>
+          <t>1100 Hubbard Rd</t>
+        </is>
+      </c>
+      <c r="E371" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F371" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G371" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H371" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-3174</t>
+        </is>
+      </c>
+      <c r="I371" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J371" s="8" t="inlineStr">
+        <is>
+          <t>signalmtnnursery.com</t>
+        </is>
+      </c>
+      <c r="K371" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L371" s="8" t="inlineStr">
+        <is>
+          <t>Third-generation family owners (names not publicly listed)</t>
+        </is>
+      </c>
+      <c r="M371" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N371" s="8" t="inlineStr">
+        <is>
+          <t>76-year operating nursery growing/delivering plants on-site; likely owns delivery trucks</t>
+        </is>
+      </c>
+      <c r="O371" s="8" t="inlineStr">
+        <is>
+          <t>Yelp (15 reviews); active Facebook page; own website</t>
+        </is>
+      </c>
+      <c r="P371" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q371" s="8" t="inlineStr">
+        <is>
+          <t>Yellow Pages</t>
+        </is>
+      </c>
+      <c r="R371" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="8" t="inlineStr">
+        <is>
+          <t>Signal Pest Control (Signal Mountain Pest Control)</t>
+        </is>
+      </c>
+      <c r="B372" s="8" t="inlineStr">
+        <is>
+          <t>Pest Control</t>
+        </is>
+      </c>
+      <c r="C372" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D372" s="8" t="inlineStr">
+        <is>
+          <t>54 Miller Cove Rd</t>
+        </is>
+      </c>
+      <c r="E372" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F372" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G372" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H372" s="8" t="inlineStr">
+        <is>
+          <t>(423) 498-4840</t>
+        </is>
+      </c>
+      <c r="I372" s="8" t="inlineStr">
+        <is>
+          <t>info@signalpest.com</t>
+        </is>
+      </c>
+      <c r="J372" s="8" t="inlineStr">
+        <is>
+          <t>signalmountainpestcontrol.com</t>
+        </is>
+      </c>
+      <c r="K372" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L372" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M372" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N372" s="8" t="inlineStr">
+        <is>
+          <t>Route-based pest techs driving daily across the mountain and into north Georgia</t>
+        </is>
+      </c>
+      <c r="O372" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing (51 photos); Manta listing</t>
+        </is>
+      </c>
+      <c r="P372" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q372" s="8" t="inlineStr">
+        <is>
+          <t>Manta business listing</t>
+        </is>
+      </c>
+      <c r="R372" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain Cleaners</t>
+        </is>
+      </c>
+      <c r="B373" s="8" t="inlineStr">
+        <is>
+          <t>Dry Cleaning / Laundry</t>
+        </is>
+      </c>
+      <c r="C373" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="inlineStr">
+        <is>
+          <t>821 Mississippi Ave</t>
+        </is>
+      </c>
+      <c r="E373" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F373" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G373" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H373" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-1371</t>
+        </is>
+      </c>
+      <c r="I373" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J373" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K373" s="8" t="inlineStr">
+        <is>
+          <t>Nanci Kelly</t>
+        </is>
+      </c>
+      <c r="L373" s="8" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="M373" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N373" s="8" t="inlineStr">
+        <is>
+          <t>Long-running local business (since 1958); possible pickup/delivery route vehicle</t>
+        </is>
+      </c>
+      <c r="O373" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile (A+ rating)</t>
+        </is>
+      </c>
+      <c r="P373" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q373" s="8" t="inlineStr">
+        <is>
+          <t>Birdeye reviews</t>
+        </is>
+      </c>
+      <c r="R373" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="8" t="inlineStr">
+        <is>
+          <t>CR Paint Inc</t>
+        </is>
+      </c>
+      <c r="B374" s="8" t="inlineStr">
+        <is>
+          <t>Painting Contractor</t>
+        </is>
+      </c>
+      <c r="C374" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D374" s="8" t="inlineStr">
+        <is>
+          <t>1506 Layton Ln</t>
+        </is>
+      </c>
+      <c r="E374" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F374" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G374" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H374" s="8" t="inlineStr">
+        <is>
+          <t>(423) 779-7907</t>
+        </is>
+      </c>
+      <c r="I374" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J374" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K374" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L374" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M374" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N374" s="8" t="inlineStr">
+        <is>
+          <t>Painting crews travel to multiple job sites daily with loaded trucks</t>
+        </is>
+      </c>
+      <c r="O374" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp listing</t>
+        </is>
+      </c>
+      <c r="P374" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q374" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R374" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="8" t="inlineStr">
+        <is>
+          <t>Elder's Ace Hardware</t>
+        </is>
+      </c>
+      <c r="B375" s="8" t="inlineStr">
+        <is>
+          <t>Hardware Store</t>
+        </is>
+      </c>
+      <c r="C375" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D375" s="8" t="inlineStr">
+        <is>
+          <t>2000 Taft Hwy</t>
+        </is>
+      </c>
+      <c r="E375" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F375" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G375" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H375" s="8" t="inlineStr">
+        <is>
+          <t>(423) 517-0177</t>
+        </is>
+      </c>
+      <c r="I375" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J375" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K375" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L375" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M375" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N375" s="8" t="inlineStr">
+        <is>
+          <t>Ace Hardware locations commonly run delivery trucks and curbside/contractor-delivery service</t>
+        </is>
+      </c>
+      <c r="O375" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing; Benjamin Moore store locator listing</t>
+        </is>
+      </c>
+      <c r="P375" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q375" s="8" t="inlineStr">
+        <is>
+          <t>Benjamin Moore store locator</t>
+        </is>
+      </c>
+      <c r="R375" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="8" t="inlineStr">
+        <is>
+          <t>Mountain Service Imports</t>
+        </is>
+      </c>
+      <c r="B376" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C376" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D376" s="8" t="inlineStr">
+        <is>
+          <t>800 Signal Mountain Blvd</t>
+        </is>
+      </c>
+      <c r="E376" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F376" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G376" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H376" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-2414</t>
+        </is>
+      </c>
+      <c r="I376" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J376" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K376" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L376" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M376" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N376" s="8" t="inlineStr">
+        <is>
+          <t>Auto repair shop with loaner/shuttle/tow vehicles; potential referral partner for glass replacement overflow</t>
+        </is>
+      </c>
+      <c r="O376" s="8" t="inlineStr">
+        <is>
+          <t>BBB Business Profile (Auto Repair category)</t>
+        </is>
+      </c>
+      <c r="P376" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q376" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R376" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="8" t="inlineStr">
+        <is>
+          <t>Maples Automotive</t>
+        </is>
+      </c>
+      <c r="B377" s="8" t="inlineStr">
+        <is>
+          <t>Auto Repair</t>
+        </is>
+      </c>
+      <c r="C377" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D377" s="8" t="inlineStr">
+        <is>
+          <t>462 Miller Rd</t>
+        </is>
+      </c>
+      <c r="E377" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F377" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G377" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H377" s="8" t="inlineStr">
+        <is>
+          <t>(423) 596-9384</t>
+        </is>
+      </c>
+      <c r="I377" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J377" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K377" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L377" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M377" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N377" s="8" t="inlineStr">
+        <is>
+          <t>Independent auto shop likely running shop/tow vehicles; possible referral partner</t>
+        </is>
+      </c>
+      <c r="O377" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing (13 photos)</t>
+        </is>
+      </c>
+      <c r="P377" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q377" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R377" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="8" t="inlineStr">
+        <is>
+          <t>Welch Dental Center, PLLC</t>
+        </is>
+      </c>
+      <c r="B378" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C378" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D378" s="8" t="inlineStr">
+        <is>
+          <t>1408 James Blvd</t>
+        </is>
+      </c>
+      <c r="E378" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F378" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G378" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H378" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-3649</t>
+        </is>
+      </c>
+      <c r="I378" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J378" s="8" t="inlineStr">
+        <is>
+          <t>welchdds.com</t>
+        </is>
+      </c>
+      <c r="K378" s="8" t="inlineStr">
+        <is>
+          <t>Larry G. Welch, DDS / Jonathan R. Welch, DDS</t>
+        </is>
+      </c>
+      <c r="L378" s="8" t="inlineStr">
+        <is>
+          <t>Dentists / Owners</t>
+        </is>
+      </c>
+      <c r="M378" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N378" s="8" t="inlineStr">
+        <is>
+          <t>Established multi-dentist practice; decision-makers are local business owners, good relationship/referral prospect</t>
+        </is>
+      </c>
+      <c r="O378" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile; ADA Find-a-Dentist listing</t>
+        </is>
+      </c>
+      <c r="P378" s="8" t="inlineStr">
+        <is>
+          <t>BBB profile</t>
+        </is>
+      </c>
+      <c r="Q378" s="8" t="inlineStr">
+        <is>
+          <t>ADA Find a Dentist</t>
+        </is>
+      </c>
+      <c r="R378" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="8" t="inlineStr">
+        <is>
+          <t>Sawrie Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C379" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D379" s="8" t="inlineStr">
+        <is>
+          <t>1807 Taft Hwy, Suite 4</t>
+        </is>
+      </c>
+      <c r="E379" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F379" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G379" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H379" s="8" t="inlineStr">
+        <is>
+          <t>(423) 777-4393</t>
+        </is>
+      </c>
+      <c r="I379" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J379" s="8" t="inlineStr">
+        <is>
+          <t>sawriedental.com</t>
+        </is>
+      </c>
+      <c r="K379" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L379" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M379" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N379" s="8" t="inlineStr">
+        <is>
+          <t>Local practice owner is a potential decision-maker for staff-vehicle service and referrals</t>
+        </is>
+      </c>
+      <c r="O379" s="8" t="inlineStr">
+        <is>
+          <t>Practice's own About page</t>
+        </is>
+      </c>
+      <c r="P379" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q379" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R379" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="8" t="inlineStr">
+        <is>
+          <t>Gipsy Gourmet Catering</t>
+        </is>
+      </c>
+      <c r="B380" s="8" t="inlineStr">
+        <is>
+          <t>Catering / Restaurant</t>
+        </is>
+      </c>
+      <c r="C380" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D380" s="8" t="inlineStr">
+        <is>
+          <t>1309 Taft Hwy, Ste 139</t>
+        </is>
+      </c>
+      <c r="E380" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F380" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G380" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H380" s="8" t="inlineStr">
+        <is>
+          <t>(423) 250-3039</t>
+        </is>
+      </c>
+      <c r="I380" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J380" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K380" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L380" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M380" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N380" s="8" t="inlineStr">
+        <is>
+          <t>Catering business requires delivery vehicles making frequent runs, higher chip/crack exposure</t>
+        </is>
+      </c>
+      <c r="O380" s="8" t="inlineStr">
+        <is>
+          <t>Active Yelp caterer listing</t>
+        </is>
+      </c>
+      <c r="P380" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q380" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R380" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="8" t="inlineStr">
+        <is>
+          <t>Pruett's Market</t>
+        </is>
+      </c>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Grocery Store</t>
+        </is>
+      </c>
+      <c r="C381" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D381" s="8" t="inlineStr">
+        <is>
+          <t>1210 Taft Hwy</t>
+        </is>
+      </c>
+      <c r="E381" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F381" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G381" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H381" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-2044</t>
+        </is>
+      </c>
+      <c r="I381" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J381" s="8" t="inlineStr">
+        <is>
+          <t>pruettsmarket.com</t>
+        </is>
+      </c>
+      <c r="K381" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L381" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M381" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N381" s="8" t="inlineStr">
+        <is>
+          <t>Community grocery chain location likely using delivery/supply vehicles between stores</t>
+        </is>
+      </c>
+      <c r="O381" s="8" t="inlineStr">
+        <is>
+          <t>Own multi-location website</t>
+        </is>
+      </c>
+      <c r="P381" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q381" s="8" t="inlineStr">
+        <is>
+          <t>Business directory listing</t>
+        </is>
+      </c>
+      <c r="R381" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="8" t="inlineStr">
+        <is>
+          <t>Educare Day Care &amp; Learning Center</t>
+        </is>
+      </c>
+      <c r="B382" s="8" t="inlineStr">
+        <is>
+          <t>Child Care / Daycare</t>
+        </is>
+      </c>
+      <c r="C382" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D382" s="8" t="inlineStr">
+        <is>
+          <t>4305 Taft Hwy</t>
+        </is>
+      </c>
+      <c r="E382" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F382" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G382" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H382" s="8" t="inlineStr">
+        <is>
+          <t>(423) 517-0065</t>
+        </is>
+      </c>
+      <c r="I382" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J382" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K382" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L382" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M382" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N382" s="8" t="inlineStr">
+        <is>
+          <t>Child care centers commonly operate a van for field trips/transport</t>
+        </is>
+      </c>
+      <c r="O382" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing; TN DHS active provider directory</t>
+        </is>
+      </c>
+      <c r="P382" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q382" s="8" t="inlineStr">
+        <is>
+          <t>TN Dept. of Human Services provider directory</t>
+        </is>
+      </c>
+      <c r="R382" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain Presbyterian Church</t>
+        </is>
+      </c>
+      <c r="B383" s="8" t="inlineStr">
+        <is>
+          <t>Religious Organization / School (Presbyterian Day School)</t>
+        </is>
+      </c>
+      <c r="C383" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D383" s="8" t="inlineStr">
+        <is>
+          <t>612 James Blvd</t>
+        </is>
+      </c>
+      <c r="E383" s="8" t="inlineStr">
+        <is>
+          <t>Signal Mountain</t>
+        </is>
+      </c>
+      <c r="F383" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G383" s="8" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="H383" s="8" t="inlineStr">
+        <is>
+          <t>(423) 886-2190</t>
+        </is>
+      </c>
+      <c r="I383" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J383" s="8" t="inlineStr">
+        <is>
+          <t>signalpres.org</t>
+        </is>
+      </c>
+      <c r="K383" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L383" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M383" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N383" s="8" t="inlineStr">
+        <is>
+          <t>Large congregation with an attached preschool ministry; likely operates van(s) for ministry/transport</t>
+        </is>
+      </c>
+      <c r="O383" s="8" t="inlineStr">
+        <is>
+          <t>Own website; active Facebook/LinkedIn pages</t>
+        </is>
+      </c>
+      <c r="P383" s="8" t="inlineStr">
+        <is>
+          <t>Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="Q383" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="R383" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain Dental</t>
+        </is>
+      </c>
+      <c r="B384" s="8" t="inlineStr">
+        <is>
+          <t>Dental Practice</t>
+        </is>
+      </c>
+      <c r="C384" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D384" s="8" t="inlineStr">
+        <is>
+          <t>120 N Watauga Ln</t>
+        </is>
+      </c>
+      <c r="E384" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F384" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G384" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H384" s="8" t="inlineStr">
+        <is>
+          <t>(423) 821-7508</t>
+        </is>
+      </c>
+      <c r="I384" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J384" s="8" t="inlineStr">
+        <is>
+          <t>lookoutmountaindental.com</t>
+        </is>
+      </c>
+      <c r="K384" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L384" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M384" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N384" s="8" t="inlineStr">
+        <is>
+          <t>Established local practice; decision-maker relationship/referral prospect</t>
+        </is>
+      </c>
+      <c r="O384" s="8" t="inlineStr">
+        <is>
+          <t>Own website with contact page</t>
+        </is>
+      </c>
+      <c r="P384" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q384" s="8" t="inlineStr">
+        <is>
+          <t>Healthgrades practice listing</t>
+        </is>
+      </c>
+      <c r="R384" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="8" t="inlineStr">
+        <is>
+          <t>Market on the Mountain</t>
+        </is>
+      </c>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>Grocery / Specialty Market</t>
+        </is>
+      </c>
+      <c r="C385" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D385" s="8" t="inlineStr">
+        <is>
+          <t>812 Scenic Hwy</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F385" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G385" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H385" s="8" t="inlineStr">
+        <is>
+          <t>(423) 821-5150</t>
+        </is>
+      </c>
+      <c r="I385" s="8" t="inlineStr">
+        <is>
+          <t>marketonthemtn@gmail.com</t>
+        </is>
+      </c>
+      <c r="J385" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K385" s="8" t="inlineStr">
+        <is>
+          <t>Ruth (last name not publicly available)</t>
+        </is>
+      </c>
+      <c r="L385" s="8" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="M385" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N385" s="8" t="inlineStr">
+        <is>
+          <t>Small local market/deli likely running a supply or delivery vehicle; long daily hours signal active, steady business</t>
+        </is>
+      </c>
+      <c r="O385" s="8" t="inlineStr">
+        <is>
+          <t>Yelp (18 reviews); Tripadvisor listing</t>
+        </is>
+      </c>
+      <c r="P385" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q385" s="8" t="inlineStr">
+        <is>
+          <t>Tripadvisor listing</t>
+        </is>
+      </c>
+      <c r="R385" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="8" t="inlineStr">
+        <is>
+          <t>Woodall Agency Insurance</t>
+        </is>
+      </c>
+      <c r="B386" s="8" t="inlineStr">
+        <is>
+          <t>Insurance Agency</t>
+        </is>
+      </c>
+      <c r="C386" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D386" s="8" t="inlineStr">
+        <is>
+          <t>431 W Brow Rd</t>
+        </is>
+      </c>
+      <c r="E386" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F386" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G386" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H386" s="8" t="inlineStr">
+        <is>
+          <t>(423) 266-6716</t>
+        </is>
+      </c>
+      <c r="I386" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J386" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="K386" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L386" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M386" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N386" s="8" t="inlineStr">
+        <is>
+          <t>Independent local agency principal is a decision-maker/referral source for personal-vehicle and small-fleet clients</t>
+        </is>
+      </c>
+      <c r="O386" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="P386" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q386" s="8" t="inlineStr">
+        <is>
+          <t>Bar List Publishing independent agents directory</t>
+        </is>
+      </c>
+      <c r="R386" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain Presbyterian Church</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>Religious Organization</t>
+        </is>
+      </c>
+      <c r="C387" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>316 N Bragg Ave</t>
+        </is>
+      </c>
+      <c r="E387" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F387" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G387" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H387" s="8" t="inlineStr">
+        <is>
+          <t>(423) 821-4528</t>
+        </is>
+      </c>
+      <c r="I387" s="8" t="inlineStr">
+        <is>
+          <t>info@lmpc.org</t>
+        </is>
+      </c>
+      <c r="J387" s="8" t="inlineStr">
+        <is>
+          <t>lmpc.org</t>
+        </is>
+      </c>
+      <c r="K387" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L387" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M387" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N387" s="8" t="inlineStr">
+        <is>
+          <t>Sizeable established congregation; churches of this scale commonly run van(s) for ministry/youth transport</t>
+        </is>
+      </c>
+      <c r="O387" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing; GuideStar nonprofit profile</t>
+        </is>
+      </c>
+      <c r="P387" s="8" t="inlineStr">
+        <is>
+          <t>Yelp listing</t>
+        </is>
+      </c>
+      <c r="Q387" s="8" t="inlineStr">
+        <is>
+          <t>GuideStar profile</t>
+        </is>
+      </c>
+      <c r="R387" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="8" t="inlineStr">
+        <is>
+          <t>Christ Reformed Baptist Church</t>
+        </is>
+      </c>
+      <c r="B388" s="8" t="inlineStr">
+        <is>
+          <t>Religious Organization</t>
+        </is>
+      </c>
+      <c r="C388" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D388" s="8" t="inlineStr">
+        <is>
+          <t>901 Scenic Hwy</t>
+        </is>
+      </c>
+      <c r="E388" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F388" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G388" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H388" s="8" t="inlineStr">
+        <is>
+          <t>(423) 521-2628</t>
+        </is>
+      </c>
+      <c r="I388" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J388" s="8" t="inlineStr">
+        <is>
+          <t>crbchattanooga.org</t>
+        </is>
+      </c>
+      <c r="K388" s="8" t="inlineStr">
+        <is>
+          <t>Nathan White</t>
+        </is>
+      </c>
+      <c r="L388" s="8" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="M388" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N388" s="8" t="inlineStr">
+        <is>
+          <t>Smaller church plant (constituted 2019); lower fleet likelihood but confirmed active with a real address/phone</t>
+        </is>
+      </c>
+      <c r="O388" s="8" t="inlineStr">
+        <is>
+          <t>Own website with times/location page</t>
+        </is>
+      </c>
+      <c r="P388" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q388" s="8" t="inlineStr">
+        <is>
+          <t>SermonAudio broadcaster profile</t>
+        </is>
+      </c>
+      <c r="R388" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="8" t="inlineStr">
+        <is>
+          <t>Church of the Good Shepherd (Episcopal) / Good Shepherd School</t>
+        </is>
+      </c>
+      <c r="B389" s="8" t="inlineStr">
+        <is>
+          <t>Religious Organization / Preschool</t>
+        </is>
+      </c>
+      <c r="C389" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D389" s="8" t="inlineStr">
+        <is>
+          <t>211 Franklin Rd</t>
+        </is>
+      </c>
+      <c r="E389" s="8" t="inlineStr">
+        <is>
+          <t>Lookout Mountain</t>
+        </is>
+      </c>
+      <c r="F389" s="8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="G389" s="8" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="H389" s="8" t="inlineStr">
+        <is>
+          <t>(423) 821-0044</t>
+        </is>
+      </c>
+      <c r="I389" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="J389" s="8" t="inlineStr">
+        <is>
+          <t>gslookout.org</t>
+        </is>
+      </c>
+      <c r="K389" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="L389" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly available</t>
+        </is>
+      </c>
+      <c r="M389" s="8" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
+      </c>
+      <c r="N389" s="8" t="inlineStr">
+        <is>
+          <t>Church with an attached day school (daycare through Pre-K); schools of this type often run a van for transport</t>
+        </is>
+      </c>
+      <c r="O389" s="8" t="inlineStr">
+        <is>
+          <t>Own website; Yelp listing</t>
+        </is>
+      </c>
+      <c r="P389" s="8" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="Q389" s="8" t="inlineStr">
+        <is>
+          <t>Episcopal Diocese of East TN school directory</t>
+        </is>
+      </c>
+      <c r="R389" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R286"/>
+  <autoFilter ref="A1:R389"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>